--- a/포드_models.xlsx
+++ b/포드_models.xlsx
@@ -11,7 +11,7 @@
     <sheet name="안내" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'포드 트랜스폰더 DB'!$A$1:$P$132</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'포드 트랜스폰더 DB'!$A$1:$P$108</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P132"/>
+  <dimension ref="A1:P108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3642,12 +3642,12 @@
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>GT (슈퍼카, 1세대)</t>
+          <t>이스케이프</t>
         </is>
       </c>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
@@ -3665,9 +3665,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G47" s="6" t="inlineStr">
-        <is>
-          <t>ID4C</t>
+      <c r="G47" s="9" t="inlineStr">
+        <is>
+          <t>ID60(4D60)</t>
         </is>
       </c>
       <c r="H47" s="9" t="inlineStr">
@@ -3675,11 +3675,7 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I47" s="9" t="inlineStr">
-        <is>
-          <t>011-R0221[해외 공용 품번]</t>
-        </is>
-      </c>
+      <c r="I47" s="9" t="inlineStr"/>
       <c r="J47" s="9" t="inlineStr">
         <is>
           <t>FO38</t>
@@ -3688,21 +3684,17 @@
       <c r="K47" s="9" t="inlineStr"/>
       <c r="L47" s="9" t="inlineStr"/>
       <c r="M47" s="9" t="inlineStr"/>
-      <c r="N47" s="6" t="inlineStr">
+      <c r="N47" s="9" t="inlineStr">
         <is>
           <t>PATS</t>
         </is>
       </c>
       <c r="O47" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Ford GT 2005–2006 Texas Fixed 4C, 트랜스폰더 키 Strattec 597602·598333·011-R0221 H72-PT)</t>
-        </is>
-      </c>
-      <c r="P47" s="6" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 이력 없음 — 해외(북미) 사양 기준</t>
-        </is>
-      </c>
+          <t>transpondery(Ford Catalog Escape 2001–2004 Texas Crypto 4D60, FO38), OEM 키 카탈로그(Escape 2001–2004 98AG15K601AA·AB·AC·AD 433MHz — 유럽 공용 리모컨, 국내 적용 미확인), 나무위키(이스케이프 2001년부터 국내 판매)</t>
+        </is>
+      </c>
+      <c r="P47" s="9" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="9" t="inlineStr">
@@ -3712,12 +3704,12 @@
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>GT (슈퍼카, 1세대)</t>
+          <t>이스케이프</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>2006(단종)</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
@@ -3735,9 +3727,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G48" s="6" t="inlineStr">
-        <is>
-          <t>ID4C</t>
+      <c r="G48" s="9" t="inlineStr">
+        <is>
+          <t>ID60(4D60)</t>
         </is>
       </c>
       <c r="H48" s="9" t="inlineStr">
@@ -3745,11 +3737,7 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I48" s="9" t="inlineStr">
-        <is>
-          <t>011-R0221[해외 공용 품번]</t>
-        </is>
-      </c>
+      <c r="I48" s="9" t="inlineStr"/>
       <c r="J48" s="9" t="inlineStr">
         <is>
           <t>FO38</t>
@@ -3758,21 +3746,17 @@
       <c r="K48" s="9" t="inlineStr"/>
       <c r="L48" s="9" t="inlineStr"/>
       <c r="M48" s="9" t="inlineStr"/>
-      <c r="N48" s="6" t="inlineStr">
+      <c r="N48" s="9" t="inlineStr">
         <is>
           <t>PATS</t>
         </is>
       </c>
       <c r="O48" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Ford GT 2005–2006 Texas Fixed 4C, 트랜스폰더 키 Strattec 597602·598333·011-R0221 H72-PT)</t>
-        </is>
-      </c>
-      <c r="P48" s="6" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 이력 없음 — 해외(북미) 사양 기준</t>
-        </is>
-      </c>
+          <t>transpondery(Ford Catalog Escape 2001–2004 Texas Crypto 4D60, FO38), OEM 키 카탈로그(Escape 2001–2004 98AG15K601AA·AB·AC·AD 433MHz — 유럽 공용 리모컨, 국내 적용 미확인), 나무위키(이스케이프 2001년부터 국내 판매)</t>
+        </is>
+      </c>
+      <c r="P48" s="9" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="9" t="inlineStr">
@@ -3782,22 +3766,22 @@
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>GT (슈퍼카, 2세대)</t>
+          <t>이스케이프</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
@@ -3805,40 +3789,36 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G49" s="6" t="inlineStr">
-        <is>
-          <t>ID49</t>
+      <c r="G49" s="9" t="inlineStr">
+        <is>
+          <t>ID60(4D60)</t>
         </is>
       </c>
       <c r="H49" s="9" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>막대키</t>
         </is>
       </c>
       <c r="I49" s="9" t="inlineStr"/>
       <c r="J49" s="9" t="inlineStr">
         <is>
-          <t>HU101</t>
+          <t>FO38</t>
         </is>
       </c>
       <c r="K49" s="9" t="inlineStr"/>
       <c r="L49" s="9" t="inlineStr"/>
       <c r="M49" s="9" t="inlineStr"/>
-      <c r="N49" s="6" t="inlineStr">
+      <c r="N49" s="9" t="inlineStr">
         <is>
           <t>PATS</t>
         </is>
       </c>
       <c r="O49" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Ford GT 2017–2022 HiTag Pro ID49, HU101)</t>
-        </is>
-      </c>
-      <c r="P49" s="6" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 이력 없음 — 해외(북미) 사양 기준</t>
-        </is>
-      </c>
+          <t>transpondery(Ford Catalog Escape 2001–2004 Texas Crypto 4D60, FO38), OEM 키 카탈로그(Escape 2001–2004 98AG15K601AA·AB·AC·AD 433MHz — 유럽 공용 리모컨, 국내 적용 미확인), 나무위키(이스케이프 2001년부터 국내 판매)</t>
+        </is>
+      </c>
+      <c r="P49" s="9" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="9" t="inlineStr">
@@ -3848,22 +3828,22 @@
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>GT (슈퍼카, 2세대)</t>
+          <t>이스케이프</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
@@ -3871,40 +3851,36 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G50" s="6" t="inlineStr">
-        <is>
-          <t>ID49</t>
+      <c r="G50" s="9" t="inlineStr">
+        <is>
+          <t>ID60(4D60)</t>
         </is>
       </c>
       <c r="H50" s="9" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>막대키</t>
         </is>
       </c>
       <c r="I50" s="9" t="inlineStr"/>
       <c r="J50" s="9" t="inlineStr">
         <is>
-          <t>HU101</t>
+          <t>FO38</t>
         </is>
       </c>
       <c r="K50" s="9" t="inlineStr"/>
       <c r="L50" s="9" t="inlineStr"/>
       <c r="M50" s="9" t="inlineStr"/>
-      <c r="N50" s="6" t="inlineStr">
+      <c r="N50" s="9" t="inlineStr">
         <is>
           <t>PATS</t>
         </is>
       </c>
       <c r="O50" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Ford GT 2017–2022 HiTag Pro ID49, HU101)</t>
-        </is>
-      </c>
-      <c r="P50" s="6" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 이력 없음 — 해외(북미) 사양 기준</t>
-        </is>
-      </c>
+          <t>transpondery(Ford Catalog Escape 2001–2004 Texas Crypto 4D60, FO38), OEM 키 카탈로그(Escape 2001–2004 98AG15K601AA·AB·AC·AD 433MHz — 유럽 공용 리모컨, 국내 적용 미확인), 나무위키(이스케이프 2001년부터 국내 판매)</t>
+        </is>
+      </c>
+      <c r="P50" s="9" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="9" t="inlineStr">
@@ -3914,22 +3890,22 @@
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>GT (슈퍼카, 2세대)</t>
+          <t>이스케이프</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
@@ -3937,40 +3913,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G51" s="6" t="inlineStr">
-        <is>
-          <t>ID49</t>
+      <c r="G51" s="9" t="inlineStr">
+        <is>
+          <t>ID63(4D63)</t>
         </is>
       </c>
       <c r="H51" s="9" t="inlineStr">
         <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I51" s="9" t="inlineStr"/>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="I51" s="9" t="inlineStr">
+        <is>
+          <t>164-R0475[해외 공용 품번], 164-R8040[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J51" s="9" t="inlineStr">
         <is>
-          <t>HU101</t>
+          <t>FO38</t>
         </is>
       </c>
       <c r="K51" s="9" t="inlineStr"/>
       <c r="L51" s="9" t="inlineStr"/>
       <c r="M51" s="9" t="inlineStr"/>
-      <c r="N51" s="6" t="inlineStr">
+      <c r="N51" s="9" t="inlineStr">
         <is>
           <t>PATS</t>
         </is>
       </c>
       <c r="O51" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Ford GT 2017–2022 HiTag Pro ID49, HU101)</t>
-        </is>
-      </c>
-      <c r="P51" s="6" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 이력 없음 — 해외(북미) 사양 기준</t>
-        </is>
-      </c>
+          <t>transpondery(Ford Catalog Escape 2005–2010 Texas Crypto 4D63 DST40, FO38 — 리모컨 키 164-R8007·8070은 315MHz라 뺌, 트랜스폰더 키 164-R0475·164-R8040)</t>
+        </is>
+      </c>
+      <c r="P51" s="9" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="9" t="inlineStr">
@@ -3980,22 +3956,22 @@
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>GT (슈퍼카, 2세대)</t>
+          <t>이스케이프</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>2020(단종)</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
@@ -4003,40 +3979,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G52" s="6" t="inlineStr">
-        <is>
-          <t>ID49</t>
+      <c r="G52" s="9" t="inlineStr">
+        <is>
+          <t>ID63(4D63)</t>
         </is>
       </c>
       <c r="H52" s="9" t="inlineStr">
         <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I52" s="9" t="inlineStr"/>
+          <t>막대키</t>
+        </is>
+      </c>
+      <c r="I52" s="9" t="inlineStr">
+        <is>
+          <t>164-R0475[해외 공용 품번], 164-R8040[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J52" s="9" t="inlineStr">
         <is>
-          <t>HU101</t>
+          <t>FO38</t>
         </is>
       </c>
       <c r="K52" s="9" t="inlineStr"/>
       <c r="L52" s="9" t="inlineStr"/>
       <c r="M52" s="9" t="inlineStr"/>
-      <c r="N52" s="6" t="inlineStr">
+      <c r="N52" s="9" t="inlineStr">
         <is>
           <t>PATS</t>
         </is>
       </c>
       <c r="O52" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Ford GT 2017–2022 HiTag Pro ID49, HU101)</t>
-        </is>
-      </c>
-      <c r="P52" s="6" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 이력 없음 — 해외(북미) 사양 기준</t>
-        </is>
-      </c>
+          <t>transpondery(Ford Catalog Escape 2005–2010 Texas Crypto 4D63 DST40, FO38 — 리모컨 키 164-R8007·8070은 315MHz라 뺌, 트랜스폰더 키 164-R0475·164-R8040)</t>
+        </is>
+      </c>
+      <c r="P52" s="9" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="9" t="inlineStr">
@@ -4051,7 +4027,7 @@
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
@@ -4071,7 +4047,7 @@
       </c>
       <c r="G53" s="9" t="inlineStr">
         <is>
-          <t>ID60(4D60)</t>
+          <t>ID63(4D63)</t>
         </is>
       </c>
       <c r="H53" s="9" t="inlineStr">
@@ -4079,7 +4055,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I53" s="9" t="inlineStr"/>
+      <c r="I53" s="9" t="inlineStr">
+        <is>
+          <t>164-R0475[해외 공용 품번], 164-R8040[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J53" s="9" t="inlineStr">
         <is>
           <t>FO38</t>
@@ -4095,7 +4075,7 @@
       </c>
       <c r="O53" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Escape 2001–2004 Texas Crypto 4D60, FO38), OEM 키 카탈로그(Escape 2001–2004 98AG15K601AA·AB·AC·AD 433MHz — 유럽 공용 리모컨, 국내 적용 미확인), 나무위키(이스케이프 2001년부터 국내 판매)</t>
+          <t>transpondery(Ford Catalog Escape 2005–2010 Texas Crypto 4D63 DST40, FO38 — 리모컨 키 164-R8007·8070은 315MHz라 뺌, 트랜스폰더 키 164-R0475·164-R8040)</t>
         </is>
       </c>
       <c r="P53" s="9" t="inlineStr"/>
@@ -4113,7 +4093,7 @@
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
@@ -4133,7 +4113,7 @@
       </c>
       <c r="G54" s="9" t="inlineStr">
         <is>
-          <t>ID60(4D60)</t>
+          <t>ID63(4D63)</t>
         </is>
       </c>
       <c r="H54" s="9" t="inlineStr">
@@ -4141,7 +4121,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I54" s="9" t="inlineStr"/>
+      <c r="I54" s="9" t="inlineStr">
+        <is>
+          <t>164-R0475[해외 공용 품번], 164-R8040[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J54" s="9" t="inlineStr">
         <is>
           <t>FO38</t>
@@ -4157,7 +4141,7 @@
       </c>
       <c r="O54" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Escape 2001–2004 Texas Crypto 4D60, FO38), OEM 키 카탈로그(Escape 2001–2004 98AG15K601AA·AB·AC·AD 433MHz — 유럽 공용 리모컨, 국내 적용 미확인), 나무위키(이스케이프 2001년부터 국내 판매)</t>
+          <t>transpondery(Ford Catalog Escape 2005–2010 Texas Crypto 4D63 DST40, FO38 — 리모컨 키 164-R8007·8070은 315MHz라 뺌, 트랜스폰더 키 164-R0475·164-R8040)</t>
         </is>
       </c>
       <c r="P54" s="9" t="inlineStr"/>
@@ -4175,7 +4159,7 @@
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
@@ -4195,7 +4179,7 @@
       </c>
       <c r="G55" s="9" t="inlineStr">
         <is>
-          <t>ID60(4D60)</t>
+          <t>ID63(4D63)</t>
         </is>
       </c>
       <c r="H55" s="9" t="inlineStr">
@@ -4203,7 +4187,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I55" s="9" t="inlineStr"/>
+      <c r="I55" s="9" t="inlineStr">
+        <is>
+          <t>164-R0475[해외 공용 품번], 164-R8040[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J55" s="9" t="inlineStr">
         <is>
           <t>FO38</t>
@@ -4219,7 +4207,7 @@
       </c>
       <c r="O55" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Escape 2001–2004 Texas Crypto 4D60, FO38), OEM 키 카탈로그(Escape 2001–2004 98AG15K601AA·AB·AC·AD 433MHz — 유럽 공용 리모컨, 국내 적용 미확인), 나무위키(이스케이프 2001년부터 국내 판매)</t>
+          <t>transpondery(Ford Catalog Escape 2005–2010 Texas Crypto 4D63 DST40, FO38 — 리모컨 키 164-R8007·8070은 315MHz라 뺌, 트랜스폰더 키 164-R0475·164-R8040)</t>
         </is>
       </c>
       <c r="P55" s="9" t="inlineStr"/>
@@ -4237,7 +4225,7 @@
       </c>
       <c r="C56" s="9" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
@@ -4257,7 +4245,7 @@
       </c>
       <c r="G56" s="9" t="inlineStr">
         <is>
-          <t>ID60(4D60)</t>
+          <t>ID63(4D63)</t>
         </is>
       </c>
       <c r="H56" s="9" t="inlineStr">
@@ -4265,7 +4253,11 @@
           <t>막대키</t>
         </is>
       </c>
-      <c r="I56" s="9" t="inlineStr"/>
+      <c r="I56" s="9" t="inlineStr">
+        <is>
+          <t>164-R0475[해외 공용 품번], 164-R8040[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J56" s="9" t="inlineStr">
         <is>
           <t>FO38</t>
@@ -4281,7 +4273,7 @@
       </c>
       <c r="O56" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Escape 2001–2004 Texas Crypto 4D60, FO38), OEM 키 카탈로그(Escape 2001–2004 98AG15K601AA·AB·AC·AD 433MHz — 유럽 공용 리모컨, 국내 적용 미확인), 나무위키(이스케이프 2001년부터 국내 판매)</t>
+          <t>transpondery(Ford Catalog Escape 2005–2010 Texas Crypto 4D63 DST40, FO38 — 리모컨 키 164-R8007·8070은 315MHz라 뺌, 트랜스폰더 키 164-R0475·164-R8040)</t>
         </is>
       </c>
       <c r="P56" s="9" t="inlineStr"/>
@@ -4299,7 +4291,7 @@
       </c>
       <c r="C57" s="9" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
@@ -4319,7 +4311,7 @@
       </c>
       <c r="G57" s="9" t="inlineStr">
         <is>
-          <t>ID63(4D63)</t>
+          <t>4D63x80</t>
         </is>
       </c>
       <c r="H57" s="9" t="inlineStr">
@@ -4329,7 +4321,7 @@
       </c>
       <c r="I57" s="9" t="inlineStr">
         <is>
-          <t>164-R0475[해외 공용 품번], 164-R8040[해외 공용 품번]</t>
+          <t>164-R8073[해외 공용 품번]</t>
         </is>
       </c>
       <c r="J57" s="9" t="inlineStr">
@@ -4347,7 +4339,7 @@
       </c>
       <c r="O57" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Escape 2005–2010 Texas Crypto 4D63 DST40, FO38 — 리모컨 키 164-R8007·8070은 315MHz라 뺌, 트랜스폰더 키 164-R0475·164-R8040)</t>
+          <t>transpondery(Ford Catalog Escape 2011–2012 Texas Crypto 2 DST80 80bit, 트랜스폰더 키 Strattec 5912512·164-R8073)</t>
         </is>
       </c>
       <c r="P57" s="9" t="inlineStr"/>
@@ -4365,7 +4357,7 @@
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
@@ -4385,7 +4377,7 @@
       </c>
       <c r="G58" s="9" t="inlineStr">
         <is>
-          <t>ID63(4D63)</t>
+          <t>4D63x80</t>
         </is>
       </c>
       <c r="H58" s="9" t="inlineStr">
@@ -4395,7 +4387,7 @@
       </c>
       <c r="I58" s="9" t="inlineStr">
         <is>
-          <t>164-R0475[해외 공용 품번], 164-R8040[해외 공용 품번]</t>
+          <t>164-R8073[해외 공용 품번]</t>
         </is>
       </c>
       <c r="J58" s="9" t="inlineStr">
@@ -4413,7 +4405,7 @@
       </c>
       <c r="O58" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Escape 2005–2010 Texas Crypto 4D63 DST40, FO38 — 리모컨 키 164-R8007·8070은 315MHz라 뺌, 트랜스폰더 키 164-R0475·164-R8040)</t>
+          <t>transpondery(Ford Catalog Escape 2011–2012 Texas Crypto 2 DST80 80bit, 트랜스폰더 키 Strattec 5912512·164-R8073)</t>
         </is>
       </c>
       <c r="P58" s="9" t="inlineStr"/>
@@ -4431,7 +4423,7 @@
       </c>
       <c r="C59" s="9" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
@@ -4451,22 +4443,22 @@
       </c>
       <c r="G59" s="9" t="inlineStr">
         <is>
-          <t>ID63(4D63)</t>
+          <t>4D63x80[플립키], ID46(PCF7953A)[스마트키]</t>
         </is>
       </c>
       <c r="H59" s="9" t="inlineStr">
         <is>
-          <t>막대키</t>
+          <t>폴딩키,스마트키</t>
         </is>
       </c>
       <c r="I59" s="9" t="inlineStr">
         <is>
-          <t>164-R0475[해외 공용 품번], 164-R8040[해외 공용 품번]</t>
+          <t>164-R8022[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J59" s="9" t="inlineStr">
         <is>
-          <t>FO38</t>
+          <t>HU101</t>
         </is>
       </c>
       <c r="K59" s="9" t="inlineStr"/>
@@ -4479,7 +4471,7 @@
       </c>
       <c r="O59" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Escape 2005–2010 Texas Crypto 4D63 DST40, FO38 — 리모컨 키 164-R8007·8070은 315MHz라 뺌, 트랜스폰더 키 164-R0475·164-R8040)</t>
+          <t>transpondery(Ford Catalog Escape 2013–2019 DST80 80bit 플립키(164-R8046 등 315MHz 뺌), 2013–2018 ID46 PCF7953A 스마트키(164-R8091·8092 315MHz 뺌), 비상키 164-R8022), 나무위키(2015년 말 쿠가로 대체되며 국내 판매 중단)</t>
         </is>
       </c>
       <c r="P59" s="9" t="inlineStr"/>
@@ -4497,7 +4489,7 @@
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
@@ -4517,22 +4509,22 @@
       </c>
       <c r="G60" s="9" t="inlineStr">
         <is>
-          <t>ID63(4D63)</t>
+          <t>4D63x80[플립키], ID46(PCF7953A)[스마트키]</t>
         </is>
       </c>
       <c r="H60" s="9" t="inlineStr">
         <is>
-          <t>막대키</t>
+          <t>폴딩키,스마트키</t>
         </is>
       </c>
       <c r="I60" s="9" t="inlineStr">
         <is>
-          <t>164-R0475[해외 공용 품번], 164-R8040[해외 공용 품번]</t>
+          <t>164-R8022[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J60" s="9" t="inlineStr">
         <is>
-          <t>FO38</t>
+          <t>HU101</t>
         </is>
       </c>
       <c r="K60" s="9" t="inlineStr"/>
@@ -4545,7 +4537,7 @@
       </c>
       <c r="O60" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Escape 2005–2010 Texas Crypto 4D63 DST40, FO38 — 리모컨 키 164-R8007·8070은 315MHz라 뺌, 트랜스폰더 키 164-R0475·164-R8040)</t>
+          <t>transpondery(Ford Catalog Escape 2013–2019 DST80 80bit 플립키(164-R8046 등 315MHz 뺌), 2013–2018 ID46 PCF7953A 스마트키(164-R8091·8092 315MHz 뺌), 비상키 164-R8022), 나무위키(2015년 말 쿠가로 대체되며 국내 판매 중단)</t>
         </is>
       </c>
       <c r="P60" s="9" t="inlineStr"/>
@@ -4563,7 +4555,7 @@
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2015(단종)</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
@@ -4583,22 +4575,22 @@
       </c>
       <c r="G61" s="9" t="inlineStr">
         <is>
-          <t>ID63(4D63)</t>
+          <t>4D63x80[플립키], ID46(PCF7953A)[스마트키]</t>
         </is>
       </c>
       <c r="H61" s="9" t="inlineStr">
         <is>
-          <t>막대키</t>
+          <t>폴딩키,스마트키</t>
         </is>
       </c>
       <c r="I61" s="9" t="inlineStr">
         <is>
-          <t>164-R0475[해외 공용 품번], 164-R8040[해외 공용 품번]</t>
+          <t>164-R8022[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J61" s="9" t="inlineStr">
         <is>
-          <t>FO38</t>
+          <t>HU101</t>
         </is>
       </c>
       <c r="K61" s="9" t="inlineStr"/>
@@ -4611,7 +4603,7 @@
       </c>
       <c r="O61" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Escape 2005–2010 Texas Crypto 4D63 DST40, FO38 — 리모컨 키 164-R8007·8070은 315MHz라 뺌, 트랜스폰더 키 164-R0475·164-R8040)</t>
+          <t>transpondery(Ford Catalog Escape 2013–2019 DST80 80bit 플립키(164-R8046 등 315MHz 뺌), 2013–2018 ID46 PCF7953A 스마트키(164-R8091·8092 315MHz 뺌), 비상키 164-R8022), 나무위키(2015년 말 쿠가로 대체되며 국내 판매 중단)</t>
         </is>
       </c>
       <c r="P61" s="9" t="inlineStr"/>
@@ -4624,12 +4616,12 @@
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>이스케이프</t>
+          <t>쿠가</t>
         </is>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
@@ -4649,26 +4641,26 @@
       </c>
       <c r="G62" s="9" t="inlineStr">
         <is>
-          <t>ID63(4D63)</t>
+          <t>4D63x80</t>
         </is>
       </c>
       <c r="H62" s="9" t="inlineStr">
         <is>
-          <t>막대키</t>
-        </is>
-      </c>
-      <c r="I62" s="9" t="inlineStr">
-        <is>
-          <t>164-R0475[해외 공용 품번], 164-R8040[해외 공용 품번]</t>
-        </is>
-      </c>
+          <t>폴딩키,스마트키</t>
+        </is>
+      </c>
+      <c r="I62" s="9" t="inlineStr"/>
       <c r="J62" s="9" t="inlineStr">
         <is>
-          <t>FO38</t>
+          <t>HU101</t>
         </is>
       </c>
       <c r="K62" s="9" t="inlineStr"/>
-      <c r="L62" s="9" t="inlineStr"/>
+      <c r="L62" s="9" t="inlineStr">
+        <is>
+          <t>7S7T-15K601-ED[해외 공용 품번], 7S7T-15K601-EE[해외 공용 품번], 7S7T-15K601-EF[해외 공용 품번], 7S7T-15K601-EG[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M62" s="9" t="inlineStr"/>
       <c r="N62" s="9" t="inlineStr">
         <is>
@@ -4677,7 +4669,7 @@
       </c>
       <c r="O62" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Escape 2005–2010 Texas Crypto 4D63 DST40, FO38 — 리모컨 키 164-R8007·8070은 315MHz라 뺌, 트랜스폰더 키 164-R0475·164-R8040)</t>
+          <t>transpondery(Ford Catalog Kuga MK2 2015–2016 Europe Texas Crypto 2 DST80 ID63-6F 80bit, KeyFree 스마트키 7S7T-15K601-ED·EE·EF·EG 433/434MHz), 이데일리(2015 서울모터쇼 몬데오·쿠가 국내 첫선), 모터그래프(디젤 SUV 쿠가 출시)</t>
         </is>
       </c>
       <c r="P62" s="9" t="inlineStr"/>
@@ -4690,12 +4682,12 @@
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>이스케이프</t>
+          <t>쿠가</t>
         </is>
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
@@ -4720,21 +4712,21 @@
       </c>
       <c r="H63" s="9" t="inlineStr">
         <is>
-          <t>막대키</t>
-        </is>
-      </c>
-      <c r="I63" s="9" t="inlineStr">
-        <is>
-          <t>164-R8073[해외 공용 품번]</t>
-        </is>
-      </c>
+          <t>폴딩키,스마트키</t>
+        </is>
+      </c>
+      <c r="I63" s="9" t="inlineStr"/>
       <c r="J63" s="9" t="inlineStr">
         <is>
-          <t>FO38</t>
+          <t>HU101</t>
         </is>
       </c>
       <c r="K63" s="9" t="inlineStr"/>
-      <c r="L63" s="9" t="inlineStr"/>
+      <c r="L63" s="9" t="inlineStr">
+        <is>
+          <t>7S7T-15K601-ED[해외 공용 품번], 7S7T-15K601-EE[해외 공용 품번], 7S7T-15K601-EF[해외 공용 품번], 7S7T-15K601-EG[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M63" s="9" t="inlineStr"/>
       <c r="N63" s="9" t="inlineStr">
         <is>
@@ -4743,7 +4735,7 @@
       </c>
       <c r="O63" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Escape 2011–2012 Texas Crypto 2 DST80 80bit, 트랜스폰더 키 Strattec 5912512·164-R8073)</t>
+          <t>transpondery(Ford Catalog Kuga MK2 2015–2016 Europe Texas Crypto 2 DST80 ID63-6F 80bit, KeyFree 스마트키 7S7T-15K601-ED·EE·EF·EG 433/434MHz), 이데일리(2015 서울모터쇼 몬데오·쿠가 국내 첫선), 모터그래프(디젤 SUV 쿠가 출시)</t>
         </is>
       </c>
       <c r="P63" s="9" t="inlineStr"/>
@@ -4756,22 +4748,22 @@
       </c>
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t>이스케이프</t>
+          <t>쿠가</t>
         </is>
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E64" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
@@ -4781,26 +4773,26 @@
       </c>
       <c r="G64" s="9" t="inlineStr">
         <is>
-          <t>4D63x80</t>
+          <t>ID47</t>
         </is>
       </c>
       <c r="H64" s="9" t="inlineStr">
         <is>
-          <t>막대키</t>
-        </is>
-      </c>
-      <c r="I64" s="9" t="inlineStr">
-        <is>
-          <t>164-R8073[해외 공용 품번]</t>
-        </is>
-      </c>
+          <t>폴딩키,스마트키</t>
+        </is>
+      </c>
+      <c r="I64" s="9" t="inlineStr"/>
       <c r="J64" s="9" t="inlineStr">
         <is>
-          <t>FO38</t>
+          <t>HU101</t>
         </is>
       </c>
       <c r="K64" s="9" t="inlineStr"/>
-      <c r="L64" s="9" t="inlineStr"/>
+      <c r="L64" s="9" t="inlineStr">
+        <is>
+          <t>F1ET-15K601-AE[해외 공용 품번], F1ET-15K601-AF[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M64" s="9" t="inlineStr"/>
       <c r="N64" s="9" t="inlineStr">
         <is>
@@ -4809,7 +4801,7 @@
       </c>
       <c r="O64" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Escape 2011–2012 Texas Crypto 2 DST80 80bit, 트랜스폰더 키 Strattec 5912512·164-R8073)</t>
+          <t>transpondery(Ford Catalog Kuga MK2 Facelift 2016–2019 Europe Philips Crypto 3 HiTag Pro ID47, 스마트키 F1ET-15K601-AE·AF 433/434MHz), 카가이(쿠가 국내 판매 후 단종)</t>
         </is>
       </c>
       <c r="P64" s="9" t="inlineStr"/>
@@ -4822,22 +4814,22 @@
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>이스케이프</t>
+          <t>쿠가</t>
         </is>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2018(단종)</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
@@ -4847,7 +4839,7 @@
       </c>
       <c r="G65" s="9" t="inlineStr">
         <is>
-          <t>4D63x80[플립키], ID46(PCF7953A)[스마트키]</t>
+          <t>ID47</t>
         </is>
       </c>
       <c r="H65" s="9" t="inlineStr">
@@ -4855,18 +4847,18 @@
           <t>폴딩키,스마트키</t>
         </is>
       </c>
-      <c r="I65" s="9" t="inlineStr">
-        <is>
-          <t>164-R8022[비상키, 해외 공용 품번]</t>
-        </is>
-      </c>
+      <c r="I65" s="9" t="inlineStr"/>
       <c r="J65" s="9" t="inlineStr">
         <is>
           <t>HU101</t>
         </is>
       </c>
       <c r="K65" s="9" t="inlineStr"/>
-      <c r="L65" s="9" t="inlineStr"/>
+      <c r="L65" s="9" t="inlineStr">
+        <is>
+          <t>F1ET-15K601-AE[해외 공용 품번], F1ET-15K601-AF[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M65" s="9" t="inlineStr"/>
       <c r="N65" s="9" t="inlineStr">
         <is>
@@ -4875,7 +4867,7 @@
       </c>
       <c r="O65" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Escape 2013–2019 DST80 80bit 플립키(164-R8046 등 315MHz 뺌), 2013–2018 ID46 PCF7953A 스마트키(164-R8091·8092 315MHz 뺌), 비상키 164-R8022), 나무위키(2015년 말 쿠가로 대체되며 국내 판매 중단)</t>
+          <t>transpondery(Ford Catalog Kuga MK2 Facelift 2016–2019 Europe Philips Crypto 3 HiTag Pro ID47, 스마트키 F1ET-15K601-AE·AF 433/434MHz), 카가이(쿠가 국내 판매 후 단종)</t>
         </is>
       </c>
       <c r="P65" s="9" t="inlineStr"/>
@@ -4888,22 +4880,22 @@
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>이스케이프</t>
+          <t>브롱코</t>
         </is>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F66" s="3" t="inlineStr">
@@ -4913,17 +4905,17 @@
       </c>
       <c r="G66" s="9" t="inlineStr">
         <is>
-          <t>4D63x80[플립키], ID46(PCF7953A)[스마트키]</t>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H66" s="9" t="inlineStr">
         <is>
-          <t>폴딩키,스마트키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I66" s="9" t="inlineStr">
         <is>
-          <t>164-R8022[비상키, 해외 공용 품번]</t>
+          <t>164-R8168[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J66" s="9" t="inlineStr">
@@ -4941,7 +4933,7 @@
       </c>
       <c r="O66" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Escape 2013–2019 DST80 80bit 플립키(164-R8046 등 315MHz 뺌), 2013–2018 ID46 PCF7953A 스마트키(164-R8091·8092 315MHz 뺌), 비상키 164-R8022), 나무위키(2015년 말 쿠가로 대체되며 국내 판매 중단)</t>
+          <t>transpondery(Ford Catalog Bronco 2021–2024 HiTag Pro ID49, 비상키 164-R8168 HU101 — 스마트키 164-R8295·8297·8340은 315·902MHz라 뺌), 탑라이더(브롱코 2021 국내 인증·출시)</t>
         </is>
       </c>
       <c r="P66" s="9" t="inlineStr"/>
@@ -4954,22 +4946,22 @@
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>이스케이프</t>
+          <t>브롱코</t>
         </is>
       </c>
       <c r="C67" s="9" t="inlineStr">
         <is>
-          <t>2015(단종)</t>
-        </is>
-      </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
@@ -4979,17 +4971,17 @@
       </c>
       <c r="G67" s="9" t="inlineStr">
         <is>
-          <t>4D63x80[플립키], ID46(PCF7953A)[스마트키]</t>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H67" s="9" t="inlineStr">
         <is>
-          <t>폴딩키,스마트키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I67" s="9" t="inlineStr">
         <is>
-          <t>164-R8022[비상키, 해외 공용 품번]</t>
+          <t>164-R8168[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J67" s="9" t="inlineStr">
@@ -5007,7 +4999,7 @@
       </c>
       <c r="O67" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Escape 2013–2019 DST80 80bit 플립키(164-R8046 등 315MHz 뺌), 2013–2018 ID46 PCF7953A 스마트키(164-R8091·8092 315MHz 뺌), 비상키 164-R8022), 나무위키(2015년 말 쿠가로 대체되며 국내 판매 중단)</t>
+          <t>transpondery(Ford Catalog Bronco 2021–2024 HiTag Pro ID49, 비상키 164-R8168 HU101 — 스마트키 164-R8295·8297·8340은 315·902MHz라 뺌), 탑라이더(브롱코 2021 국내 인증·출시)</t>
         </is>
       </c>
       <c r="P67" s="9" t="inlineStr"/>
@@ -5020,22 +5012,22 @@
       </c>
       <c r="B68" s="9" t="inlineStr">
         <is>
-          <t>쿠가</t>
+          <t>브롱코</t>
         </is>
       </c>
       <c r="C68" s="9" t="inlineStr">
         <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="D68" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F68" s="3" t="inlineStr">
@@ -5045,26 +5037,26 @@
       </c>
       <c r="G68" s="9" t="inlineStr">
         <is>
-          <t>4D63x80</t>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H68" s="9" t="inlineStr">
         <is>
-          <t>폴딩키,스마트키</t>
-        </is>
-      </c>
-      <c r="I68" s="9" t="inlineStr"/>
+          <t>스마트키</t>
+        </is>
+      </c>
+      <c r="I68" s="9" t="inlineStr">
+        <is>
+          <t>164-R8168[비상키, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J68" s="9" t="inlineStr">
         <is>
           <t>HU101</t>
         </is>
       </c>
       <c r="K68" s="9" t="inlineStr"/>
-      <c r="L68" s="9" t="inlineStr">
-        <is>
-          <t>7S7T-15K601-ED[해외 공용 품번], 7S7T-15K601-EE[해외 공용 품번], 7S7T-15K601-EF[해외 공용 품번], 7S7T-15K601-EG[해외 공용 품번]</t>
-        </is>
-      </c>
+      <c r="L68" s="9" t="inlineStr"/>
       <c r="M68" s="9" t="inlineStr"/>
       <c r="N68" s="9" t="inlineStr">
         <is>
@@ -5073,7 +5065,7 @@
       </c>
       <c r="O68" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Kuga MK2 2015–2016 Europe Texas Crypto 2 DST80 ID63-6F 80bit, KeyFree 스마트키 7S7T-15K601-ED·EE·EF·EG 433/434MHz), 이데일리(2015 서울모터쇼 몬데오·쿠가 국내 첫선), 모터그래프(디젤 SUV 쿠가 출시)</t>
+          <t>transpondery(Ford Catalog Bronco 2021–2024 HiTag Pro ID49, 비상키 164-R8168 HU101 — 스마트키 164-R8295·8297·8340은 315·902MHz라 뺌), 탑라이더(브롱코 2021 국내 인증·출시)</t>
         </is>
       </c>
       <c r="P68" s="9" t="inlineStr"/>
@@ -5086,22 +5078,22 @@
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>쿠가</t>
+          <t>브롱코</t>
         </is>
       </c>
       <c r="C69" s="9" t="inlineStr">
         <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
@@ -5111,26 +5103,26 @@
       </c>
       <c r="G69" s="9" t="inlineStr">
         <is>
-          <t>4D63x80</t>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H69" s="9" t="inlineStr">
         <is>
-          <t>폴딩키,스마트키</t>
-        </is>
-      </c>
-      <c r="I69" s="9" t="inlineStr"/>
+          <t>스마트키</t>
+        </is>
+      </c>
+      <c r="I69" s="9" t="inlineStr">
+        <is>
+          <t>164-R8168[비상키, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J69" s="9" t="inlineStr">
         <is>
           <t>HU101</t>
         </is>
       </c>
       <c r="K69" s="9" t="inlineStr"/>
-      <c r="L69" s="9" t="inlineStr">
-        <is>
-          <t>7S7T-15K601-ED[해외 공용 품번], 7S7T-15K601-EE[해외 공용 품번], 7S7T-15K601-EF[해외 공용 품번], 7S7T-15K601-EG[해외 공용 품번]</t>
-        </is>
-      </c>
+      <c r="L69" s="9" t="inlineStr"/>
       <c r="M69" s="9" t="inlineStr"/>
       <c r="N69" s="9" t="inlineStr">
         <is>
@@ -5139,7 +5131,7 @@
       </c>
       <c r="O69" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Kuga MK2 2015–2016 Europe Texas Crypto 2 DST80 ID63-6F 80bit, KeyFree 스마트키 7S7T-15K601-ED·EE·EF·EG 433/434MHz), 이데일리(2015 서울모터쇼 몬데오·쿠가 국내 첫선), 모터그래프(디젤 SUV 쿠가 출시)</t>
+          <t>transpondery(Ford Catalog Bronco 2021–2024 HiTag Pro ID49, 비상키 164-R8168 HU101 — 스마트키 164-R8295·8297·8340은 315·902MHz라 뺌), 탑라이더(브롱코 2021 국내 인증·출시)</t>
         </is>
       </c>
       <c r="P69" s="9" t="inlineStr"/>
@@ -5152,12 +5144,12 @@
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>쿠가</t>
+          <t>브롱코</t>
         </is>
       </c>
       <c r="C70" s="9" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
@@ -5177,15 +5169,19 @@
       </c>
       <c r="G70" s="9" t="inlineStr">
         <is>
-          <t>ID47</t>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H70" s="9" t="inlineStr">
         <is>
-          <t>폴딩키,스마트키</t>
-        </is>
-      </c>
-      <c r="I70" s="9" t="inlineStr"/>
+          <t>스마트키</t>
+        </is>
+      </c>
+      <c r="I70" s="9" t="inlineStr">
+        <is>
+          <t>164-R8168[비상키, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J70" s="9" t="inlineStr">
         <is>
           <t>HU101</t>
@@ -5194,7 +5190,7 @@
       <c r="K70" s="9" t="inlineStr"/>
       <c r="L70" s="9" t="inlineStr">
         <is>
-          <t>F1ET-15K601-AE[해외 공용 품번], F1ET-15K601-AF[해외 공용 품번]</t>
+          <t>164-R8411[해외 공용 품번], 164-R8412[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M70" s="9" t="inlineStr"/>
@@ -5205,7 +5201,7 @@
       </c>
       <c r="O70" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Kuga MK2 Facelift 2016–2019 Europe Philips Crypto 3 HiTag Pro ID47, 스마트키 F1ET-15K601-AE·AF 433/434MHz), 카가이(쿠가 국내 판매 후 단종)</t>
+          <t>transpondery(Ford Catalog Bronco 2025 HiTag Pro ID49, 스마트키 164-R8411·164-R8412 434MHz FCC M3N-A3C108397)</t>
         </is>
       </c>
       <c r="P70" s="9" t="inlineStr"/>
@@ -5218,12 +5214,12 @@
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>쿠가</t>
+          <t>브롱코</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>2018(단종)</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
@@ -5243,15 +5239,19 @@
       </c>
       <c r="G71" s="9" t="inlineStr">
         <is>
-          <t>ID47</t>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H71" s="9" t="inlineStr">
         <is>
-          <t>폴딩키,스마트키</t>
-        </is>
-      </c>
-      <c r="I71" s="9" t="inlineStr"/>
+          <t>스마트키</t>
+        </is>
+      </c>
+      <c r="I71" s="9" t="inlineStr">
+        <is>
+          <t>164-R8168[비상키, 해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J71" s="9" t="inlineStr">
         <is>
           <t>HU101</t>
@@ -5260,7 +5260,7 @@
       <c r="K71" s="9" t="inlineStr"/>
       <c r="L71" s="9" t="inlineStr">
         <is>
-          <t>F1ET-15K601-AE[해외 공용 품번], F1ET-15K601-AF[해외 공용 품번]</t>
+          <t>164-R8411[해외 공용 품번], 164-R8412[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M71" s="9" t="inlineStr"/>
@@ -5271,7 +5271,7 @@
       </c>
       <c r="O71" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Kuga MK2 Facelift 2016–2019 Europe Philips Crypto 3 HiTag Pro ID47, 스마트키 F1ET-15K601-AE·AF 433/434MHz), 카가이(쿠가 국내 판매 후 단종)</t>
+          <t>transpondery(Ford Catalog Bronco 2025 HiTag Pro ID49, 스마트키 164-R8411·164-R8412 434MHz FCC M3N-A3C108397)</t>
         </is>
       </c>
       <c r="P71" s="9" t="inlineStr"/>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>브롱코</t>
+          <t>익스플로러</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="D72" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E72" s="4" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F72" s="3" t="inlineStr">
@@ -5309,22 +5309,22 @@
       </c>
       <c r="G72" s="9" t="inlineStr">
         <is>
-          <t>ID49</t>
+          <t>ID4C</t>
         </is>
       </c>
       <c r="H72" s="9" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>막대키</t>
         </is>
       </c>
       <c r="I72" s="9" t="inlineStr">
         <is>
-          <t>164-R8168[비상키, 해외 공용 품번]</t>
+          <t>011-R0221[해외 공용 품번]</t>
         </is>
       </c>
       <c r="J72" s="9" t="inlineStr">
         <is>
-          <t>HU101</t>
+          <t>FO38</t>
         </is>
       </c>
       <c r="K72" s="9" t="inlineStr"/>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="O72" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Bronco 2021–2024 HiTag Pro ID49, 비상키 164-R8168 HU101 — 스마트키 164-R8295·8297·8340은 315·902MHz라 뺌), 탑라이더(브롱코 2021 국내 인증·출시)</t>
+          <t>transpondery(Ford Catalog Explorer 1998–mid 2001 Texas Fixed 4C, 트랜스폰더 키 011-R0221 H72-PT), 아주경제(익스플로러 1996 국내 첫 출시)</t>
         </is>
       </c>
       <c r="P72" s="9" t="inlineStr"/>
@@ -5350,22 +5350,22 @@
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>브롱코</t>
+          <t>익스플로러</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="D73" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
@@ -5373,40 +5373,44 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G73" s="9" t="inlineStr">
-        <is>
-          <t>ID49</t>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>ID4C[2001 중반 이전]</t>
         </is>
       </c>
       <c r="H73" s="9" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>막대키</t>
         </is>
       </c>
       <c r="I73" s="9" t="inlineStr">
         <is>
-          <t>164-R8168[비상키, 해외 공용 품번]</t>
+          <t>011-R0221[해외 공용 품번]</t>
         </is>
       </c>
       <c r="J73" s="9" t="inlineStr">
         <is>
-          <t>HU101</t>
+          <t>FO38</t>
         </is>
       </c>
       <c r="K73" s="9" t="inlineStr"/>
       <c r="L73" s="9" t="inlineStr"/>
       <c r="M73" s="9" t="inlineStr"/>
-      <c r="N73" s="9" t="inlineStr">
+      <c r="N73" s="6" t="inlineStr">
         <is>
           <t>PATS</t>
         </is>
       </c>
       <c r="O73" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Bronco 2021–2024 HiTag Pro ID49, 비상키 164-R8168 HU101 — 스마트키 164-R8295·8297·8340은 315·902MHz라 뺌), 탑라이더(브롱코 2021 국내 인증·출시)</t>
-        </is>
-      </c>
-      <c r="P73" s="9" t="inlineStr"/>
+          <t>transpondery(Ford Catalog Explorer 1998–mid 2001 4C → mid 2001–2003 4D60)</t>
+        </is>
+      </c>
+      <c r="P73" s="6" t="inlineStr">
+        <is>
+          <t>2001년 중반 4C→4D60 전환 — 정확한 생산 시점 자료 없음</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="9" t="inlineStr">
@@ -5416,22 +5420,22 @@
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>브롱코</t>
+          <t>익스플로러</t>
         </is>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D74" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F74" s="3" t="inlineStr">
@@ -5439,40 +5443,44 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G74" s="9" t="inlineStr">
-        <is>
-          <t>ID49</t>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>ID60(4D60)[2001 중반 이후]</t>
         </is>
       </c>
       <c r="H74" s="9" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>막대키</t>
         </is>
       </c>
       <c r="I74" s="9" t="inlineStr">
         <is>
-          <t>164-R8168[비상키, 해외 공용 품번]</t>
+          <t>164-R0475[해외 공용 품번]</t>
         </is>
       </c>
       <c r="J74" s="9" t="inlineStr">
         <is>
-          <t>HU101</t>
+          <t>FO38</t>
         </is>
       </c>
       <c r="K74" s="9" t="inlineStr"/>
       <c r="L74" s="9" t="inlineStr"/>
       <c r="M74" s="9" t="inlineStr"/>
-      <c r="N74" s="9" t="inlineStr">
+      <c r="N74" s="6" t="inlineStr">
         <is>
           <t>PATS</t>
         </is>
       </c>
       <c r="O74" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Bronco 2021–2024 HiTag Pro ID49, 비상키 164-R8168 HU101 — 스마트키 164-R8295·8297·8340은 315·902MHz라 뺌), 탑라이더(브롱코 2021 국내 인증·출시)</t>
-        </is>
-      </c>
-      <c r="P74" s="9" t="inlineStr"/>
+          <t>transpondery(Ford Catalog Explorer 1998–mid 2001 4C → mid 2001–2003 4D60)</t>
+        </is>
+      </c>
+      <c r="P74" s="6" t="inlineStr">
+        <is>
+          <t>2001년 중반 4C→4D60 전환 — 정확한 생산 시점 자료 없음</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="9" t="inlineStr">
@@ -5482,22 +5490,22 @@
       </c>
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>브롱코</t>
+          <t>익스플로러</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D75" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
@@ -5507,22 +5515,22 @@
       </c>
       <c r="G75" s="9" t="inlineStr">
         <is>
-          <t>ID49</t>
+          <t>ID60(4D60)</t>
         </is>
       </c>
       <c r="H75" s="9" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>막대키</t>
         </is>
       </c>
       <c r="I75" s="9" t="inlineStr">
         <is>
-          <t>164-R8168[비상키, 해외 공용 품번]</t>
+          <t>164-R0475[해외 공용 품번]</t>
         </is>
       </c>
       <c r="J75" s="9" t="inlineStr">
         <is>
-          <t>HU101</t>
+          <t>FO38</t>
         </is>
       </c>
       <c r="K75" s="9" t="inlineStr"/>
@@ -5535,7 +5543,7 @@
       </c>
       <c r="O75" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Bronco 2021–2024 HiTag Pro ID49, 비상키 164-R8168 HU101 — 스마트키 164-R8295·8297·8340은 315·902MHz라 뺌), 탑라이더(브롱코 2021 국내 인증·출시)</t>
+          <t>transpondery(Ford Catalog Explorer mid 2001–2003 Texas Crypto 4D60, Strattec 599114·5904287·164-R0475 H84-PT)</t>
         </is>
       </c>
       <c r="P75" s="9" t="inlineStr"/>
@@ -5548,22 +5556,22 @@
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>브롱코</t>
+          <t>익스플로러</t>
         </is>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D76" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
@@ -5573,30 +5581,26 @@
       </c>
       <c r="G76" s="9" t="inlineStr">
         <is>
-          <t>ID49</t>
+          <t>ID60(4D60)</t>
         </is>
       </c>
       <c r="H76" s="9" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>막대키</t>
         </is>
       </c>
       <c r="I76" s="9" t="inlineStr">
         <is>
-          <t>164-R8168[비상키, 해외 공용 품번]</t>
+          <t>164-R0475[해외 공용 품번]</t>
         </is>
       </c>
       <c r="J76" s="9" t="inlineStr">
         <is>
-          <t>HU101</t>
+          <t>FO38</t>
         </is>
       </c>
       <c r="K76" s="9" t="inlineStr"/>
-      <c r="L76" s="9" t="inlineStr">
-        <is>
-          <t>164-R8411[해외 공용 품번], 164-R8412[해외 공용 품번]</t>
-        </is>
-      </c>
+      <c r="L76" s="9" t="inlineStr"/>
       <c r="M76" s="9" t="inlineStr"/>
       <c r="N76" s="9" t="inlineStr">
         <is>
@@ -5605,7 +5609,7 @@
       </c>
       <c r="O76" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Bronco 2025 HiTag Pro ID49, 스마트키 164-R8411·164-R8412 434MHz FCC M3N-A3C108397)</t>
+          <t>transpondery(Ford Catalog Explorer mid 2001–2003 Texas Crypto 4D60, Strattec 599114·5904287·164-R0475 H84-PT)</t>
         </is>
       </c>
       <c r="P76" s="9" t="inlineStr"/>
@@ -5618,22 +5622,22 @@
       </c>
       <c r="B77" s="9" t="inlineStr">
         <is>
-          <t>브롱코</t>
+          <t>익스플로러</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="D77" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
@@ -5643,30 +5647,26 @@
       </c>
       <c r="G77" s="9" t="inlineStr">
         <is>
-          <t>ID49</t>
+          <t>ID63(4D63)</t>
         </is>
       </c>
       <c r="H77" s="9" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>막대키</t>
         </is>
       </c>
       <c r="I77" s="9" t="inlineStr">
         <is>
-          <t>164-R8168[비상키, 해외 공용 품번]</t>
+          <t>164-R0475[해외 공용 품번], 164-R8040[해외 공용 품번]</t>
         </is>
       </c>
       <c r="J77" s="9" t="inlineStr">
         <is>
-          <t>HU101</t>
+          <t>FO38</t>
         </is>
       </c>
       <c r="K77" s="9" t="inlineStr"/>
-      <c r="L77" s="9" t="inlineStr">
-        <is>
-          <t>164-R8411[해외 공용 품번], 164-R8412[해외 공용 품번]</t>
-        </is>
-      </c>
+      <c r="L77" s="9" t="inlineStr"/>
       <c r="M77" s="9" t="inlineStr"/>
       <c r="N77" s="9" t="inlineStr">
         <is>
@@ -5675,7 +5675,7 @@
       </c>
       <c r="O77" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Bronco 2025 HiTag Pro ID49, 스마트키 164-R8411·164-R8412 434MHz FCC M3N-A3C108397)</t>
+          <t>transpondery(Ford Catalog Explorer 2004–2010 Texas Crypto 4D63 DST40, Strattec 599114·5904287·5913441·164-R0475·164-R8040 H84-PT)</t>
         </is>
       </c>
       <c r="P77" s="9" t="inlineStr"/>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="G78" s="9" t="inlineStr">
         <is>
-          <t>ID4C</t>
+          <t>ID63(4D63)</t>
         </is>
       </c>
       <c r="H78" s="9" t="inlineStr">
@@ -5723,7 +5723,7 @@
       </c>
       <c r="I78" s="9" t="inlineStr">
         <is>
-          <t>011-R0221[해외 공용 품번]</t>
+          <t>164-R0475[해외 공용 품번], 164-R8040[해외 공용 품번]</t>
         </is>
       </c>
       <c r="J78" s="9" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="O78" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Explorer 1998–mid 2001 Texas Fixed 4C, 트랜스폰더 키 011-R0221 H72-PT), 아주경제(익스플로러 1996 국내 첫 출시)</t>
+          <t>transpondery(Ford Catalog Explorer 2004–2010 Texas Crypto 4D63 DST40, Strattec 599114·5904287·5913441·164-R0475·164-R8040 H84-PT)</t>
         </is>
       </c>
       <c r="P78" s="9" t="inlineStr"/>
@@ -5759,7 +5759,7 @@
       </c>
       <c r="C79" s="9" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
@@ -5777,9 +5777,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G79" s="6" t="inlineStr">
-        <is>
-          <t>ID4C[2001 중반 이전]</t>
+      <c r="G79" s="9" t="inlineStr">
+        <is>
+          <t>ID63(4D63)</t>
         </is>
       </c>
       <c r="H79" s="9" t="inlineStr">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="I79" s="9" t="inlineStr">
         <is>
-          <t>011-R0221[해외 공용 품번]</t>
+          <t>164-R0475[해외 공용 품번], 164-R8040[해외 공용 품번]</t>
         </is>
       </c>
       <c r="J79" s="9" t="inlineStr">
@@ -5800,21 +5800,17 @@
       <c r="K79" s="9" t="inlineStr"/>
       <c r="L79" s="9" t="inlineStr"/>
       <c r="M79" s="9" t="inlineStr"/>
-      <c r="N79" s="6" t="inlineStr">
+      <c r="N79" s="9" t="inlineStr">
         <is>
           <t>PATS</t>
         </is>
       </c>
       <c r="O79" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Explorer 1998–mid 2001 4C → mid 2001–2003 4D60)</t>
-        </is>
-      </c>
-      <c r="P79" s="6" t="inlineStr">
-        <is>
-          <t>2001년 중반 4C→4D60 전환 — 정확한 생산 시점 자료 없음</t>
-        </is>
-      </c>
+          <t>transpondery(Ford Catalog Explorer 2004–2010 Texas Crypto 4D63 DST40, Strattec 599114·5904287·5913441·164-R0475·164-R8040 H84-PT)</t>
+        </is>
+      </c>
+      <c r="P79" s="9" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="9" t="inlineStr">
@@ -5829,7 +5825,7 @@
       </c>
       <c r="C80" s="9" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="D80" s="3" t="inlineStr">
@@ -5847,9 +5843,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G80" s="6" t="inlineStr">
-        <is>
-          <t>ID60(4D60)[2001 중반 이후]</t>
+      <c r="G80" s="9" t="inlineStr">
+        <is>
+          <t>ID63(4D63)</t>
         </is>
       </c>
       <c r="H80" s="9" t="inlineStr">
@@ -5859,7 +5855,7 @@
       </c>
       <c r="I80" s="9" t="inlineStr">
         <is>
-          <t>164-R0475[해외 공용 품번]</t>
+          <t>164-R0475[해외 공용 품번], 164-R8040[해외 공용 품번]</t>
         </is>
       </c>
       <c r="J80" s="9" t="inlineStr">
@@ -5870,21 +5866,17 @@
       <c r="K80" s="9" t="inlineStr"/>
       <c r="L80" s="9" t="inlineStr"/>
       <c r="M80" s="9" t="inlineStr"/>
-      <c r="N80" s="6" t="inlineStr">
+      <c r="N80" s="9" t="inlineStr">
         <is>
           <t>PATS</t>
         </is>
       </c>
       <c r="O80" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Explorer 1998–mid 2001 4C → mid 2001–2003 4D60)</t>
-        </is>
-      </c>
-      <c r="P80" s="6" t="inlineStr">
-        <is>
-          <t>2001년 중반 4C→4D60 전환 — 정확한 생산 시점 자료 없음</t>
-        </is>
-      </c>
+          <t>transpondery(Ford Catalog Explorer 2004–2010 Texas Crypto 4D63 DST40, Strattec 599114·5904287·5913441·164-R0475·164-R8040 H84-PT)</t>
+        </is>
+      </c>
+      <c r="P80" s="9" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="9" t="inlineStr">
@@ -5899,7 +5891,7 @@
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="D81" s="3" t="inlineStr">
@@ -5919,7 +5911,7 @@
       </c>
       <c r="G81" s="9" t="inlineStr">
         <is>
-          <t>ID60(4D60)</t>
+          <t>ID63(4D63)</t>
         </is>
       </c>
       <c r="H81" s="9" t="inlineStr">
@@ -5929,7 +5921,7 @@
       </c>
       <c r="I81" s="9" t="inlineStr">
         <is>
-          <t>164-R0475[해외 공용 품번]</t>
+          <t>164-R0475[해외 공용 품번], 164-R8040[해외 공용 품번]</t>
         </is>
       </c>
       <c r="J81" s="9" t="inlineStr">
@@ -5947,7 +5939,7 @@
       </c>
       <c r="O81" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Explorer mid 2001–2003 Texas Crypto 4D60, Strattec 599114·5904287·164-R0475 H84-PT)</t>
+          <t>transpondery(Ford Catalog Explorer 2004–2010 Texas Crypto 4D63 DST40, Strattec 599114·5904287·5913441·164-R0475·164-R8040 H84-PT)</t>
         </is>
       </c>
       <c r="P81" s="9" t="inlineStr"/>
@@ -5965,7 +5957,7 @@
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="D82" s="3" t="inlineStr">
@@ -5985,7 +5977,7 @@
       </c>
       <c r="G82" s="9" t="inlineStr">
         <is>
-          <t>ID60(4D60)</t>
+          <t>ID63(4D63)</t>
         </is>
       </c>
       <c r="H82" s="9" t="inlineStr">
@@ -5995,7 +5987,7 @@
       </c>
       <c r="I82" s="9" t="inlineStr">
         <is>
-          <t>164-R0475[해외 공용 품번]</t>
+          <t>164-R0475[해외 공용 품번], 164-R8040[해외 공용 품번]</t>
         </is>
       </c>
       <c r="J82" s="9" t="inlineStr">
@@ -6013,7 +6005,7 @@
       </c>
       <c r="O82" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Explorer mid 2001–2003 Texas Crypto 4D60, Strattec 599114·5904287·164-R0475 H84-PT)</t>
+          <t>transpondery(Ford Catalog Explorer 2004–2010 Texas Crypto 4D63 DST40, Strattec 599114·5904287·5913441·164-R0475·164-R8040 H84-PT)</t>
         </is>
       </c>
       <c r="P82" s="9" t="inlineStr"/>
@@ -6031,7 +6023,7 @@
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="D83" s="3" t="inlineStr">
@@ -6097,7 +6089,7 @@
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="D84" s="3" t="inlineStr">
@@ -6117,22 +6109,22 @@
       </c>
       <c r="G84" s="9" t="inlineStr">
         <is>
-          <t>ID63(4D63)</t>
+          <t>4D63x80[일반 키], ID46(PCF7953A)[스마트키]</t>
         </is>
       </c>
       <c r="H84" s="9" t="inlineStr">
         <is>
-          <t>막대키</t>
+          <t>막대키,스마트키</t>
         </is>
       </c>
       <c r="I84" s="9" t="inlineStr">
         <is>
-          <t>164-R0475[해외 공용 품번], 164-R8040[해외 공용 품번]</t>
+          <t>164-R8041[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J84" s="9" t="inlineStr">
         <is>
-          <t>FO38</t>
+          <t>FO38, HU101</t>
         </is>
       </c>
       <c r="K84" s="9" t="inlineStr"/>
@@ -6145,7 +6137,7 @@
       </c>
       <c r="O84" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Explorer 2004–2010 Texas Crypto 4D63 DST40, Strattec 599114·5904287·5913441·164-R0475·164-R8040 H84-PT)</t>
+          <t>transpondery(Ford Catalog Explorer 2011–2015 DST80 ID63-6F 80bit 일반 키(164-R8067 IKT 315MHz 뺌), ID46 PCF7953A PEPS 스마트키(164-R8092 315MHz 뺌), 82홈 비상키 164-R8041)</t>
         </is>
       </c>
       <c r="P84" s="9" t="inlineStr"/>
@@ -6163,7 +6155,7 @@
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="D85" s="3" t="inlineStr">
@@ -6183,22 +6175,22 @@
       </c>
       <c r="G85" s="9" t="inlineStr">
         <is>
-          <t>ID63(4D63)</t>
+          <t>4D63x80[일반 키], ID46(PCF7953A)[스마트키]</t>
         </is>
       </c>
       <c r="H85" s="9" t="inlineStr">
         <is>
-          <t>막대키</t>
+          <t>막대키,스마트키</t>
         </is>
       </c>
       <c r="I85" s="9" t="inlineStr">
         <is>
-          <t>164-R0475[해외 공용 품번], 164-R8040[해외 공용 품번]</t>
+          <t>164-R8041[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J85" s="9" t="inlineStr">
         <is>
-          <t>FO38</t>
+          <t>FO38, HU101</t>
         </is>
       </c>
       <c r="K85" s="9" t="inlineStr"/>
@@ -6211,7 +6203,7 @@
       </c>
       <c r="O85" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Explorer 2004–2010 Texas Crypto 4D63 DST40, Strattec 599114·5904287·5913441·164-R0475·164-R8040 H84-PT)</t>
+          <t>transpondery(Ford Catalog Explorer 2011–2015 DST80 ID63-6F 80bit 일반 키(164-R8067 IKT 315MHz 뺌), ID46 PCF7953A PEPS 스마트키(164-R8092 315MHz 뺌), 82홈 비상키 164-R8041)</t>
         </is>
       </c>
       <c r="P85" s="9" t="inlineStr"/>
@@ -6229,7 +6221,7 @@
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="D86" s="3" t="inlineStr">
@@ -6249,22 +6241,22 @@
       </c>
       <c r="G86" s="9" t="inlineStr">
         <is>
-          <t>ID63(4D63)</t>
+          <t>4D63x80[일반 키], ID46(PCF7953A)[스마트키]</t>
         </is>
       </c>
       <c r="H86" s="9" t="inlineStr">
         <is>
-          <t>막대키</t>
+          <t>막대키,스마트키</t>
         </is>
       </c>
       <c r="I86" s="9" t="inlineStr">
         <is>
-          <t>164-R0475[해외 공용 품번], 164-R8040[해외 공용 품번]</t>
+          <t>164-R8041[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J86" s="9" t="inlineStr">
         <is>
-          <t>FO38</t>
+          <t>FO38, HU101</t>
         </is>
       </c>
       <c r="K86" s="9" t="inlineStr"/>
@@ -6277,7 +6269,7 @@
       </c>
       <c r="O86" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Explorer 2004–2010 Texas Crypto 4D63 DST40, Strattec 599114·5904287·5913441·164-R0475·164-R8040 H84-PT)</t>
+          <t>transpondery(Ford Catalog Explorer 2011–2015 DST80 ID63-6F 80bit 일반 키(164-R8067 IKT 315MHz 뺌), ID46 PCF7953A PEPS 스마트키(164-R8092 315MHz 뺌), 82홈 비상키 164-R8041)</t>
         </is>
       </c>
       <c r="P86" s="9" t="inlineStr"/>
@@ -6295,7 +6287,7 @@
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="D87" s="3" t="inlineStr">
@@ -6315,22 +6307,22 @@
       </c>
       <c r="G87" s="9" t="inlineStr">
         <is>
-          <t>ID63(4D63)</t>
+          <t>4D63x80[일반 키], ID46(PCF7953A)[스마트키]</t>
         </is>
       </c>
       <c r="H87" s="9" t="inlineStr">
         <is>
-          <t>막대키</t>
+          <t>막대키,스마트키</t>
         </is>
       </c>
       <c r="I87" s="9" t="inlineStr">
         <is>
-          <t>164-R0475[해외 공용 품번], 164-R8040[해외 공용 품번]</t>
+          <t>164-R8041[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J87" s="9" t="inlineStr">
         <is>
-          <t>FO38</t>
+          <t>FO38, HU101</t>
         </is>
       </c>
       <c r="K87" s="9" t="inlineStr"/>
@@ -6343,7 +6335,7 @@
       </c>
       <c r="O87" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Explorer 2004–2010 Texas Crypto 4D63 DST40, Strattec 599114·5904287·5913441·164-R0475·164-R8040 H84-PT)</t>
+          <t>transpondery(Ford Catalog Explorer 2011–2015 DST80 ID63-6F 80bit 일반 키(164-R8067 IKT 315MHz 뺌), ID46 PCF7953A PEPS 스마트키(164-R8092 315MHz 뺌), 82홈 비상키 164-R8041)</t>
         </is>
       </c>
       <c r="P87" s="9" t="inlineStr"/>
@@ -6361,7 +6353,7 @@
       </c>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="D88" s="3" t="inlineStr">
@@ -6381,22 +6373,22 @@
       </c>
       <c r="G88" s="9" t="inlineStr">
         <is>
-          <t>ID63(4D63)</t>
+          <t>4D63x80[일반 키], ID46(PCF7953A)[스마트키]</t>
         </is>
       </c>
       <c r="H88" s="9" t="inlineStr">
         <is>
-          <t>막대키</t>
+          <t>막대키,스마트키</t>
         </is>
       </c>
       <c r="I88" s="9" t="inlineStr">
         <is>
-          <t>164-R0475[해외 공용 품번], 164-R8040[해외 공용 품번]</t>
+          <t>164-R8041[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J88" s="9" t="inlineStr">
         <is>
-          <t>FO38</t>
+          <t>FO38, HU101</t>
         </is>
       </c>
       <c r="K88" s="9" t="inlineStr"/>
@@ -6409,7 +6401,7 @@
       </c>
       <c r="O88" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Explorer 2004–2010 Texas Crypto 4D63 DST40, Strattec 599114·5904287·5913441·164-R0475·164-R8040 H84-PT)</t>
+          <t>transpondery(Ford Catalog Explorer 2011–2015 DST80 ID63-6F 80bit 일반 키(164-R8067 IKT 315MHz 뺌), ID46 PCF7953A PEPS 스마트키(164-R8092 315MHz 뺌), 82홈 비상키 164-R8041)</t>
         </is>
       </c>
       <c r="P88" s="9" t="inlineStr"/>
@@ -6427,17 +6419,17 @@
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="D89" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E89" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
@@ -6447,22 +6439,22 @@
       </c>
       <c r="G89" s="9" t="inlineStr">
         <is>
-          <t>ID63(4D63)</t>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H89" s="9" t="inlineStr">
         <is>
-          <t>막대키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I89" s="9" t="inlineStr">
         <is>
-          <t>164-R0475[해외 공용 품번], 164-R8040[해외 공용 품번]</t>
+          <t>164-R8168[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J89" s="9" t="inlineStr">
         <is>
-          <t>FO38</t>
+          <t>HU101</t>
         </is>
       </c>
       <c r="K89" s="9" t="inlineStr"/>
@@ -6475,7 +6467,7 @@
       </c>
       <c r="O89" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Explorer 2004–2010 Texas Crypto 4D63 DST40, Strattec 599114·5904287·5913441·164-R0475·164-R8040 H84-PT)</t>
+          <t>transpondery(Ford Catalog Explorer 2016–2017 HiTag Pro ID49(스마트키 164-R8141 868MHz, 164-R8150 315MHz 뺌), 2017–2022 비상키 164-R8168 HU101)</t>
         </is>
       </c>
       <c r="P89" s="9" t="inlineStr"/>
@@ -6493,17 +6485,17 @@
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="D90" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E90" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
@@ -6513,22 +6505,22 @@
       </c>
       <c r="G90" s="9" t="inlineStr">
         <is>
-          <t>4D63x80[일반 키], ID46(PCF7953A)[스마트키]</t>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H90" s="9" t="inlineStr">
         <is>
-          <t>막대키,스마트키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I90" s="9" t="inlineStr">
         <is>
-          <t>164-R8041[비상키, 해외 공용 품번]</t>
+          <t>164-R8168[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J90" s="9" t="inlineStr">
         <is>
-          <t>FO38, HU101</t>
+          <t>HU101</t>
         </is>
       </c>
       <c r="K90" s="9" t="inlineStr"/>
@@ -6541,7 +6533,7 @@
       </c>
       <c r="O90" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Explorer 2011–2015 DST80 ID63-6F 80bit 일반 키(164-R8067 IKT 315MHz 뺌), ID46 PCF7953A PEPS 스마트키(164-R8092 315MHz 뺌), 82홈 비상키 164-R8041)</t>
+          <t>transpondery(Ford Catalog Explorer 2016–2017 HiTag Pro ID49(스마트키 164-R8141 868MHz, 164-R8150 315MHz 뺌), 2017–2022 비상키 164-R8168 HU101)</t>
         </is>
       </c>
       <c r="P90" s="9" t="inlineStr"/>
@@ -6559,17 +6551,17 @@
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="D91" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E91" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
@@ -6579,26 +6571,30 @@
       </c>
       <c r="G91" s="9" t="inlineStr">
         <is>
-          <t>4D63x80[일반 키], ID46(PCF7953A)[스마트키]</t>
+          <t>ID49(NCF2951F)</t>
         </is>
       </c>
       <c r="H91" s="9" t="inlineStr">
         <is>
-          <t>막대키,스마트키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I91" s="9" t="inlineStr">
         <is>
-          <t>164-R8041[비상키, 해외 공용 품번]</t>
+          <t>164-R8168[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J91" s="9" t="inlineStr">
         <is>
-          <t>FO38, HU101</t>
+          <t>HU101</t>
         </is>
       </c>
       <c r="K91" s="9" t="inlineStr"/>
-      <c r="L91" s="9" t="inlineStr"/>
+      <c r="L91" s="9" t="inlineStr">
+        <is>
+          <t>164-R8151[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M91" s="9" t="inlineStr"/>
       <c r="N91" s="9" t="inlineStr">
         <is>
@@ -6607,7 +6603,7 @@
       </c>
       <c r="O91" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Explorer 2011–2015 DST80 ID63-6F 80bit 일반 키(164-R8067 IKT 315MHz 뺌), ID46 PCF7953A PEPS 스마트키(164-R8092 315MHz 뺌), 82홈 비상키 164-R8041)</t>
+          <t>transpondery(Ford Catalog Explorer 2018–2022 HiTag Pro ID49 NCF2951F, 스마트키 164-R8151 FCC M3N-A2C93142100 434MHz, 비상키 164-R8168), OEM 키 카탈로그(Explorer 2018–2020 HC3T-15K601-DB 434MHz), 6세대 국내 2019 출시</t>
         </is>
       </c>
       <c r="P91" s="9" t="inlineStr"/>
@@ -6625,17 +6621,17 @@
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="D92" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E92" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
@@ -6645,26 +6641,30 @@
       </c>
       <c r="G92" s="9" t="inlineStr">
         <is>
-          <t>4D63x80[일반 키], ID46(PCF7953A)[스마트키]</t>
+          <t>ID49(NCF2951F)</t>
         </is>
       </c>
       <c r="H92" s="9" t="inlineStr">
         <is>
-          <t>막대키,스마트키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I92" s="9" t="inlineStr">
         <is>
-          <t>164-R8041[비상키, 해외 공용 품번]</t>
+          <t>164-R8168[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J92" s="9" t="inlineStr">
         <is>
-          <t>FO38, HU101</t>
+          <t>HU101</t>
         </is>
       </c>
       <c r="K92" s="9" t="inlineStr"/>
-      <c r="L92" s="9" t="inlineStr"/>
+      <c r="L92" s="9" t="inlineStr">
+        <is>
+          <t>164-R8151[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M92" s="9" t="inlineStr"/>
       <c r="N92" s="9" t="inlineStr">
         <is>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="O92" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Explorer 2011–2015 DST80 ID63-6F 80bit 일반 키(164-R8067 IKT 315MHz 뺌), ID46 PCF7953A PEPS 스마트키(164-R8092 315MHz 뺌), 82홈 비상키 164-R8041)</t>
+          <t>transpondery(Ford Catalog Explorer 2018–2022 HiTag Pro ID49 NCF2951F, 스마트키 164-R8151 FCC M3N-A2C93142100 434MHz, 비상키 164-R8168), OEM 키 카탈로그(Explorer 2018–2020 HC3T-15K601-DB 434MHz), 6세대 국내 2019 출시</t>
         </is>
       </c>
       <c r="P92" s="9" t="inlineStr"/>
@@ -6691,17 +6691,17 @@
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="D93" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E93" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
@@ -6711,26 +6711,30 @@
       </c>
       <c r="G93" s="9" t="inlineStr">
         <is>
-          <t>4D63x80[일반 키], ID46(PCF7953A)[스마트키]</t>
+          <t>ID49(NCF2951F)</t>
         </is>
       </c>
       <c r="H93" s="9" t="inlineStr">
         <is>
-          <t>막대키,스마트키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I93" s="9" t="inlineStr">
         <is>
-          <t>164-R8041[비상키, 해외 공용 품번]</t>
+          <t>164-R8168[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J93" s="9" t="inlineStr">
         <is>
-          <t>FO38, HU101</t>
+          <t>HU101</t>
         </is>
       </c>
       <c r="K93" s="9" t="inlineStr"/>
-      <c r="L93" s="9" t="inlineStr"/>
+      <c r="L93" s="9" t="inlineStr">
+        <is>
+          <t>164-R8151[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M93" s="9" t="inlineStr"/>
       <c r="N93" s="9" t="inlineStr">
         <is>
@@ -6739,7 +6743,7 @@
       </c>
       <c r="O93" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Explorer 2011–2015 DST80 ID63-6F 80bit 일반 키(164-R8067 IKT 315MHz 뺌), ID46 PCF7953A PEPS 스마트키(164-R8092 315MHz 뺌), 82홈 비상키 164-R8041)</t>
+          <t>transpondery(Ford Catalog Explorer 2018–2022 HiTag Pro ID49 NCF2951F, 스마트키 164-R8151 FCC M3N-A2C93142100 434MHz, 비상키 164-R8168), OEM 키 카탈로그(Explorer 2018–2020 HC3T-15K601-DB 434MHz), 6세대 국내 2019 출시</t>
         </is>
       </c>
       <c r="P93" s="9" t="inlineStr"/>
@@ -6757,17 +6761,17 @@
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="D94" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E94" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
@@ -6777,26 +6781,30 @@
       </c>
       <c r="G94" s="9" t="inlineStr">
         <is>
-          <t>4D63x80[일반 키], ID46(PCF7953A)[스마트키]</t>
+          <t>ID49(NCF2951F)</t>
         </is>
       </c>
       <c r="H94" s="9" t="inlineStr">
         <is>
-          <t>막대키,스마트키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I94" s="9" t="inlineStr">
         <is>
-          <t>164-R8041[비상키, 해외 공용 품번]</t>
+          <t>164-R8168[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J94" s="9" t="inlineStr">
         <is>
-          <t>FO38, HU101</t>
+          <t>HU101</t>
         </is>
       </c>
       <c r="K94" s="9" t="inlineStr"/>
-      <c r="L94" s="9" t="inlineStr"/>
+      <c r="L94" s="9" t="inlineStr">
+        <is>
+          <t>164-R8151[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M94" s="9" t="inlineStr"/>
       <c r="N94" s="9" t="inlineStr">
         <is>
@@ -6805,7 +6813,7 @@
       </c>
       <c r="O94" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Explorer 2011–2015 DST80 ID63-6F 80bit 일반 키(164-R8067 IKT 315MHz 뺌), ID46 PCF7953A PEPS 스마트키(164-R8092 315MHz 뺌), 82홈 비상키 164-R8041)</t>
+          <t>transpondery(Ford Catalog Explorer 2018–2022 HiTag Pro ID49 NCF2951F, 스마트키 164-R8151 FCC M3N-A2C93142100 434MHz, 비상키 164-R8168), OEM 키 카탈로그(Explorer 2018–2020 HC3T-15K601-DB 434MHz), 6세대 국내 2019 출시</t>
         </is>
       </c>
       <c r="P94" s="9" t="inlineStr"/>
@@ -6823,7 +6831,7 @@
       </c>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
@@ -6843,7 +6851,7 @@
       </c>
       <c r="G95" s="9" t="inlineStr">
         <is>
-          <t>ID49</t>
+          <t>ID49(NCF2951F)</t>
         </is>
       </c>
       <c r="H95" s="9" t="inlineStr">
@@ -6862,7 +6870,11 @@
         </is>
       </c>
       <c r="K95" s="9" t="inlineStr"/>
-      <c r="L95" s="9" t="inlineStr"/>
+      <c r="L95" s="9" t="inlineStr">
+        <is>
+          <t>164-R8151[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M95" s="9" t="inlineStr"/>
       <c r="N95" s="9" t="inlineStr">
         <is>
@@ -6871,7 +6883,7 @@
       </c>
       <c r="O95" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Explorer 2016–2017 HiTag Pro ID49(스마트키 164-R8141 868MHz, 164-R8150 315MHz 뺌), 2017–2022 비상키 164-R8168 HU101)</t>
+          <t>transpondery(Ford Catalog Explorer 2018–2022 HiTag Pro ID49 NCF2951F, 스마트키 164-R8151 FCC M3N-A2C93142100 434MHz, 비상키 164-R8168), OEM 키 카탈로그(Explorer 2018–2020 HC3T-15K601-DB 434MHz), 6세대 국내 2019 출시</t>
         </is>
       </c>
       <c r="P95" s="9" t="inlineStr"/>
@@ -6889,7 +6901,7 @@
       </c>
       <c r="C96" s="9" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
@@ -6909,7 +6921,7 @@
       </c>
       <c r="G96" s="9" t="inlineStr">
         <is>
-          <t>ID49</t>
+          <t>ID49(NCF2951F)</t>
         </is>
       </c>
       <c r="H96" s="9" t="inlineStr">
@@ -6928,7 +6940,11 @@
         </is>
       </c>
       <c r="K96" s="9" t="inlineStr"/>
-      <c r="L96" s="9" t="inlineStr"/>
+      <c r="L96" s="9" t="inlineStr">
+        <is>
+          <t>164-R8151[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M96" s="9" t="inlineStr"/>
       <c r="N96" s="9" t="inlineStr">
         <is>
@@ -6937,7 +6953,7 @@
       </c>
       <c r="O96" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Explorer 2016–2017 HiTag Pro ID49(스마트키 164-R8141 868MHz, 164-R8150 315MHz 뺌), 2017–2022 비상키 164-R8168 HU101)</t>
+          <t>transpondery(Ford Catalog Explorer 2018–2022 HiTag Pro ID49 NCF2951F, 스마트키 164-R8151 FCC M3N-A2C93142100 434MHz, 비상키 164-R8168), OEM 키 카탈로그(Explorer 2018–2020 HC3T-15K601-DB 434MHz), 6세대 국내 2019 출시</t>
         </is>
       </c>
       <c r="P96" s="9" t="inlineStr"/>
@@ -6955,7 +6971,7 @@
       </c>
       <c r="C97" s="9" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
@@ -6996,7 +7012,7 @@
       <c r="K97" s="9" t="inlineStr"/>
       <c r="L97" s="9" t="inlineStr">
         <is>
-          <t>164-R8151[해외 공용 품번]</t>
+          <t>164-R8363[해외 공용 품번], 164-R8369[해외 공용 품번], 164-R8397[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M97" s="9" t="inlineStr"/>
@@ -7007,7 +7023,7 @@
       </c>
       <c r="O97" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Explorer 2018–2022 HiTag Pro ID49 NCF2951F, 스마트키 164-R8151 FCC M3N-A2C93142100 434MHz, 비상키 164-R8168), OEM 키 카탈로그(Explorer 2018–2020 HC3T-15K601-DB 434MHz), 6세대 국내 2019 출시</t>
+          <t>transpondery(Ford Catalog Explorer 2024–2025 HiTag Pro ID49, 스마트키 164-R8363·164-R8369·164-R8397 434MHz Gen 5 PEPS), 다나와(더 뉴 익스플로러 2024.11.12 국내 출시)</t>
         </is>
       </c>
       <c r="P97" s="9" t="inlineStr"/>
@@ -7025,7 +7041,7 @@
       </c>
       <c r="C98" s="9" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
@@ -7066,7 +7082,7 @@
       <c r="K98" s="9" t="inlineStr"/>
       <c r="L98" s="9" t="inlineStr">
         <is>
-          <t>164-R8151[해외 공용 품번]</t>
+          <t>164-R8363[해외 공용 품번], 164-R8369[해외 공용 품번], 164-R8397[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M98" s="9" t="inlineStr"/>
@@ -7077,7 +7093,7 @@
       </c>
       <c r="O98" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Explorer 2018–2022 HiTag Pro ID49 NCF2951F, 스마트키 164-R8151 FCC M3N-A2C93142100 434MHz, 비상키 164-R8168), OEM 키 카탈로그(Explorer 2018–2020 HC3T-15K601-DB 434MHz), 6세대 국내 2019 출시</t>
+          <t>transpondery(Ford Catalog Explorer 2024–2025 HiTag Pro ID49, 스마트키 164-R8363·164-R8369·164-R8397 434MHz Gen 5 PEPS), 다나와(더 뉴 익스플로러 2024.11.12 국내 출시)</t>
         </is>
       </c>
       <c r="P98" s="9" t="inlineStr"/>
@@ -7095,7 +7111,7 @@
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
@@ -7136,7 +7152,7 @@
       <c r="K99" s="9" t="inlineStr"/>
       <c r="L99" s="9" t="inlineStr">
         <is>
-          <t>164-R8151[해외 공용 품번]</t>
+          <t>164-R8363[해외 공용 품번], 164-R8369[해외 공용 품번], 164-R8397[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M99" s="9" t="inlineStr"/>
@@ -7147,7 +7163,7 @@
       </c>
       <c r="O99" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Explorer 2018–2022 HiTag Pro ID49 NCF2951F, 스마트키 164-R8151 FCC M3N-A2C93142100 434MHz, 비상키 164-R8168), OEM 키 카탈로그(Explorer 2018–2020 HC3T-15K601-DB 434MHz), 6세대 국내 2019 출시</t>
+          <t>transpondery(Ford Catalog Explorer 2024–2025 HiTag Pro ID49, 스마트키 164-R8363·164-R8369·164-R8397 434MHz Gen 5 PEPS), 다나와(더 뉴 익스플로러 2024.11.12 국내 출시)</t>
         </is>
       </c>
       <c r="P99" s="9" t="inlineStr"/>
@@ -7160,22 +7176,22 @@
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>익스플로러</t>
+          <t>프리스타일</t>
         </is>
       </c>
       <c r="C100" s="9" t="inlineStr">
         <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="D100" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E100" s="4" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
@@ -7185,30 +7201,26 @@
       </c>
       <c r="G100" s="9" t="inlineStr">
         <is>
-          <t>ID49(NCF2951F)</t>
+          <t>ID63(4D63)</t>
         </is>
       </c>
       <c r="H100" s="9" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>막대키</t>
         </is>
       </c>
       <c r="I100" s="9" t="inlineStr">
         <is>
-          <t>164-R8168[비상키, 해외 공용 품번]</t>
+          <t>164-R0475[해외 공용 품번]</t>
         </is>
       </c>
       <c r="J100" s="9" t="inlineStr">
         <is>
-          <t>HU101</t>
+          <t>FO38</t>
         </is>
       </c>
       <c r="K100" s="9" t="inlineStr"/>
-      <c r="L100" s="9" t="inlineStr">
-        <is>
-          <t>164-R8151[해외 공용 품번]</t>
-        </is>
-      </c>
+      <c r="L100" s="9" t="inlineStr"/>
       <c r="M100" s="9" t="inlineStr"/>
       <c r="N100" s="9" t="inlineStr">
         <is>
@@ -7217,7 +7229,7 @@
       </c>
       <c r="O100" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Explorer 2018–2022 HiTag Pro ID49 NCF2951F, 스마트키 164-R8151 FCC M3N-A2C93142100 434MHz, 비상키 164-R8168), OEM 키 카탈로그(Explorer 2018–2020 HC3T-15K601-DB 434MHz), 6세대 국내 2019 출시</t>
+          <t>transpondery(Ford Catalog Five Hundred 2005–2007·Taurus X 2008–2009 Texas Crypto 4D63 DST40 — 프리스타일은 파이브 헌드레드 왜건형, 트랜스폰더 키 164-R0475)</t>
         </is>
       </c>
       <c r="P100" s="9" t="inlineStr"/>
@@ -7230,22 +7242,22 @@
       </c>
       <c r="B101" s="9" t="inlineStr">
         <is>
-          <t>익스플로러</t>
+          <t>프리스타일</t>
         </is>
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="D101" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E101" s="4" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F101" s="3" t="inlineStr">
@@ -7255,30 +7267,26 @@
       </c>
       <c r="G101" s="9" t="inlineStr">
         <is>
-          <t>ID49(NCF2951F)</t>
+          <t>ID63(4D63)</t>
         </is>
       </c>
       <c r="H101" s="9" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>막대키</t>
         </is>
       </c>
       <c r="I101" s="9" t="inlineStr">
         <is>
-          <t>164-R8168[비상키, 해외 공용 품번]</t>
+          <t>164-R0475[해외 공용 품번]</t>
         </is>
       </c>
       <c r="J101" s="9" t="inlineStr">
         <is>
-          <t>HU101</t>
+          <t>FO38</t>
         </is>
       </c>
       <c r="K101" s="9" t="inlineStr"/>
-      <c r="L101" s="9" t="inlineStr">
-        <is>
-          <t>164-R8151[해외 공용 품번]</t>
-        </is>
-      </c>
+      <c r="L101" s="9" t="inlineStr"/>
       <c r="M101" s="9" t="inlineStr"/>
       <c r="N101" s="9" t="inlineStr">
         <is>
@@ -7287,7 +7295,7 @@
       </c>
       <c r="O101" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Explorer 2018–2022 HiTag Pro ID49 NCF2951F, 스마트키 164-R8151 FCC M3N-A2C93142100 434MHz, 비상키 164-R8168), OEM 키 카탈로그(Explorer 2018–2020 HC3T-15K601-DB 434MHz), 6세대 국내 2019 출시</t>
+          <t>transpondery(Ford Catalog Five Hundred 2005–2007·Taurus X 2008–2009 Texas Crypto 4D63 DST40 — 프리스타일은 파이브 헌드레드 왜건형, 트랜스폰더 키 164-R0475)</t>
         </is>
       </c>
       <c r="P101" s="9" t="inlineStr"/>
@@ -7300,22 +7308,22 @@
       </c>
       <c r="B102" s="9" t="inlineStr">
         <is>
-          <t>익스플로러</t>
+          <t>프리스타일</t>
         </is>
       </c>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D102" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E102" s="4" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2007(단종)</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
@@ -7325,30 +7333,26 @@
       </c>
       <c r="G102" s="9" t="inlineStr">
         <is>
-          <t>ID49(NCF2951F)</t>
+          <t>ID63(4D63)</t>
         </is>
       </c>
       <c r="H102" s="9" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>막대키</t>
         </is>
       </c>
       <c r="I102" s="9" t="inlineStr">
         <is>
-          <t>164-R8168[비상키, 해외 공용 품번]</t>
+          <t>164-R0475[해외 공용 품번]</t>
         </is>
       </c>
       <c r="J102" s="9" t="inlineStr">
         <is>
-          <t>HU101</t>
+          <t>FO38</t>
         </is>
       </c>
       <c r="K102" s="9" t="inlineStr"/>
-      <c r="L102" s="9" t="inlineStr">
-        <is>
-          <t>164-R8151[해외 공용 품번]</t>
-        </is>
-      </c>
+      <c r="L102" s="9" t="inlineStr"/>
       <c r="M102" s="9" t="inlineStr"/>
       <c r="N102" s="9" t="inlineStr">
         <is>
@@ -7357,7 +7361,7 @@
       </c>
       <c r="O102" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Explorer 2018–2022 HiTag Pro ID49 NCF2951F, 스마트키 164-R8151 FCC M3N-A2C93142100 434MHz, 비상키 164-R8168), OEM 키 카탈로그(Explorer 2018–2020 HC3T-15K601-DB 434MHz), 6세대 국내 2019 출시</t>
+          <t>transpondery(Ford Catalog Five Hundred 2005–2007·Taurus X 2008–2009 Texas Crypto 4D63 DST40 — 프리스타일은 파이브 헌드레드 왜건형, 트랜스폰더 키 164-R0475)</t>
         </is>
       </c>
       <c r="P102" s="9" t="inlineStr"/>
@@ -7370,12 +7374,12 @@
       </c>
       <c r="B103" s="9" t="inlineStr">
         <is>
-          <t>익스플로러</t>
+          <t>레인저</t>
         </is>
       </c>
       <c r="C103" s="9" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
@@ -7395,31 +7399,27 @@
       </c>
       <c r="G103" s="9" t="inlineStr">
         <is>
-          <t>ID49(NCF2951F)</t>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H103" s="9" t="inlineStr">
         <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I103" s="9" t="inlineStr">
-        <is>
-          <t>164-R8168[비상키, 해외 공용 품번]</t>
-        </is>
-      </c>
+          <t>폴딩키</t>
+        </is>
+      </c>
+      <c r="I103" s="9" t="inlineStr"/>
       <c r="J103" s="9" t="inlineStr">
         <is>
           <t>HU101</t>
         </is>
       </c>
       <c r="K103" s="9" t="inlineStr"/>
-      <c r="L103" s="9" t="inlineStr">
-        <is>
-          <t>164-R8363[해외 공용 품번], 164-R8369[해외 공용 품번], 164-R8397[해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="M103" s="9" t="inlineStr"/>
+      <c r="L103" s="9" t="inlineStr"/>
+      <c r="M103" s="9" t="inlineStr">
+        <is>
+          <t>EB3T-15K601-BA[해외 공용 품번], EB3T-15K601-BB[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="N103" s="9" t="inlineStr">
         <is>
           <t>PATS</t>
@@ -7427,7 +7427,7 @@
       </c>
       <c r="O103" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Explorer 2024–2025 HiTag Pro ID49, 스마트키 164-R8363·164-R8369·164-R8397 434MHz Gen 5 PEPS), 다나와(더 뉴 익스플로러 2024.11.12 국내 출시)</t>
+          <t>transpondery(Ford Catalog Ranger T6 Facelift 2015–2022 Europe·Australia HiTag Pro ID49, 플립키 EB3T-15K601-BA·BB 434MHz FSK), 아주경제(레인저 2021.4.12 국내 첫 출시)</t>
         </is>
       </c>
       <c r="P103" s="9" t="inlineStr"/>
@@ -7440,12 +7440,12 @@
       </c>
       <c r="B104" s="9" t="inlineStr">
         <is>
-          <t>익스플로러</t>
+          <t>레인저</t>
         </is>
       </c>
       <c r="C104" s="9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
@@ -7465,31 +7465,27 @@
       </c>
       <c r="G104" s="9" t="inlineStr">
         <is>
-          <t>ID49(NCF2951F)</t>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H104" s="9" t="inlineStr">
         <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I104" s="9" t="inlineStr">
-        <is>
-          <t>164-R8168[비상키, 해외 공용 품번]</t>
-        </is>
-      </c>
+          <t>폴딩키</t>
+        </is>
+      </c>
+      <c r="I104" s="9" t="inlineStr"/>
       <c r="J104" s="9" t="inlineStr">
         <is>
           <t>HU101</t>
         </is>
       </c>
       <c r="K104" s="9" t="inlineStr"/>
-      <c r="L104" s="9" t="inlineStr">
-        <is>
-          <t>164-R8363[해외 공용 품번], 164-R8369[해외 공용 품번], 164-R8397[해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="M104" s="9" t="inlineStr"/>
+      <c r="L104" s="9" t="inlineStr"/>
+      <c r="M104" s="9" t="inlineStr">
+        <is>
+          <t>EB3T-15K601-BA[해외 공용 품번], EB3T-15K601-BB[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="N104" s="9" t="inlineStr">
         <is>
           <t>PATS</t>
@@ -7497,7 +7493,7 @@
       </c>
       <c r="O104" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Explorer 2024–2025 HiTag Pro ID49, 스마트키 164-R8363·164-R8369·164-R8397 434MHz Gen 5 PEPS), 다나와(더 뉴 익스플로러 2024.11.12 국내 출시)</t>
+          <t>transpondery(Ford Catalog Ranger T6 Facelift 2015–2022 Europe·Australia HiTag Pro ID49, 플립키 EB3T-15K601-BA·BB 434MHz FSK), 아주경제(레인저 2021.4.12 국내 첫 출시)</t>
         </is>
       </c>
       <c r="P104" s="9" t="inlineStr"/>
@@ -7510,12 +7506,12 @@
       </c>
       <c r="B105" s="9" t="inlineStr">
         <is>
-          <t>익스플로러</t>
+          <t>레인저</t>
         </is>
       </c>
       <c r="C105" s="9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
@@ -7535,31 +7531,35 @@
       </c>
       <c r="G105" s="9" t="inlineStr">
         <is>
-          <t>ID49(NCF2951F)</t>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H105" s="9" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>폴딩키,스마트키</t>
         </is>
       </c>
       <c r="I105" s="9" t="inlineStr">
         <is>
-          <t>164-R8168[비상키, 해외 공용 품번]</t>
+          <t>164-R8267[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J105" s="9" t="inlineStr">
         <is>
-          <t>HU101</t>
+          <t>HU198</t>
         </is>
       </c>
       <c r="K105" s="9" t="inlineStr"/>
       <c r="L105" s="9" t="inlineStr">
         <is>
-          <t>164-R8363[해외 공용 품번], 164-R8369[해외 공용 품번], 164-R8397[해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="M105" s="9" t="inlineStr"/>
+          <t>164-R8406[랩터, 해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="M105" s="9" t="inlineStr">
+        <is>
+          <t>164-R8337[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="N105" s="9" t="inlineStr">
         <is>
           <t>PATS</t>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="O105" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Explorer 2024–2025 HiTag Pro ID49, 스마트키 164-R8363·164-R8369·164-R8397 434MHz Gen 5 PEPS), 다나와(더 뉴 익스플로러 2024.11.12 국내 출시)</t>
+          <t>transpondery(Ford Catalog Next-Gen Ranger·Raptor 2023–2025 HiTag Pro ID49, 플립키 164-R8337 434MHz(2025), 랩터 스마트키 164-R8406 434MHz, 센터밀 비상키 164-R8267 HU198), 다나와(신형 레인저 국내 출시)</t>
         </is>
       </c>
       <c r="P105" s="9" t="inlineStr"/>
@@ -7580,22 +7580,22 @@
       </c>
       <c r="B106" s="9" t="inlineStr">
         <is>
-          <t>프리스타일</t>
+          <t>레인저</t>
         </is>
       </c>
       <c r="C106" s="9" t="inlineStr">
         <is>
-          <t>2005</t>
-        </is>
-      </c>
-      <c r="D106" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E106" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D106" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
@@ -7605,27 +7605,35 @@
       </c>
       <c r="G106" s="9" t="inlineStr">
         <is>
-          <t>ID63(4D63)</t>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H106" s="9" t="inlineStr">
         <is>
-          <t>막대키</t>
+          <t>폴딩키,스마트키</t>
         </is>
       </c>
       <c r="I106" s="9" t="inlineStr">
         <is>
-          <t>164-R0475[해외 공용 품번]</t>
+          <t>164-R8267[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J106" s="9" t="inlineStr">
         <is>
-          <t>FO38</t>
+          <t>HU198</t>
         </is>
       </c>
       <c r="K106" s="9" t="inlineStr"/>
-      <c r="L106" s="9" t="inlineStr"/>
-      <c r="M106" s="9" t="inlineStr"/>
+      <c r="L106" s="9" t="inlineStr">
+        <is>
+          <t>164-R8406[랩터, 해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="M106" s="9" t="inlineStr">
+        <is>
+          <t>164-R8337[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="N106" s="9" t="inlineStr">
         <is>
           <t>PATS</t>
@@ -7633,7 +7641,7 @@
       </c>
       <c r="O106" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Five Hundred 2005–2007·Taurus X 2008–2009 Texas Crypto 4D63 DST40 — 프리스타일은 파이브 헌드레드 왜건형, 트랜스폰더 키 164-R0475)</t>
+          <t>transpondery(Ford Catalog Next-Gen Ranger·Raptor 2023–2025 HiTag Pro ID49, 플립키 164-R8337 434MHz(2025), 랩터 스마트키 164-R8406 434MHz, 센터밀 비상키 164-R8267 HU198), 다나와(신형 레인저 국내 출시)</t>
         </is>
       </c>
       <c r="P106" s="9" t="inlineStr"/>
@@ -7646,22 +7654,22 @@
       </c>
       <c r="B107" s="9" t="inlineStr">
         <is>
-          <t>프리스타일</t>
+          <t>레인저</t>
         </is>
       </c>
       <c r="C107" s="9" t="inlineStr">
         <is>
-          <t>2006</t>
-        </is>
-      </c>
-      <c r="D107" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E107" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F107" s="3" t="inlineStr">
@@ -7671,27 +7679,35 @@
       </c>
       <c r="G107" s="9" t="inlineStr">
         <is>
-          <t>ID63(4D63)</t>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H107" s="9" t="inlineStr">
         <is>
-          <t>막대키</t>
+          <t>폴딩키,스마트키</t>
         </is>
       </c>
       <c r="I107" s="9" t="inlineStr">
         <is>
-          <t>164-R0475[해외 공용 품번]</t>
+          <t>164-R8267[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J107" s="9" t="inlineStr">
         <is>
-          <t>FO38</t>
+          <t>HU198</t>
         </is>
       </c>
       <c r="K107" s="9" t="inlineStr"/>
-      <c r="L107" s="9" t="inlineStr"/>
-      <c r="M107" s="9" t="inlineStr"/>
+      <c r="L107" s="9" t="inlineStr">
+        <is>
+          <t>164-R8406[랩터, 해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="M107" s="9" t="inlineStr">
+        <is>
+          <t>164-R8337[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="N107" s="9" t="inlineStr">
         <is>
           <t>PATS</t>
@@ -7699,7 +7715,7 @@
       </c>
       <c r="O107" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Five Hundred 2005–2007·Taurus X 2008–2009 Texas Crypto 4D63 DST40 — 프리스타일은 파이브 헌드레드 왜건형, 트랜스폰더 키 164-R0475)</t>
+          <t>transpondery(Ford Catalog Next-Gen Ranger·Raptor 2023–2025 HiTag Pro ID49, 플립키 164-R8337 434MHz(2025), 랩터 스마트키 164-R8406 434MHz, 센터밀 비상키 164-R8267 HU198), 다나와(신형 레인저 국내 출시)</t>
         </is>
       </c>
       <c r="P107" s="9" t="inlineStr"/>
@@ -7712,22 +7728,22 @@
       </c>
       <c r="B108" s="9" t="inlineStr">
         <is>
-          <t>프리스타일</t>
+          <t>레인저</t>
         </is>
       </c>
       <c r="C108" s="9" t="inlineStr">
         <is>
-          <t>2007(단종)</t>
-        </is>
-      </c>
-      <c r="D108" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E108" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F108" s="3" t="inlineStr">
@@ -7737,27 +7753,35 @@
       </c>
       <c r="G108" s="9" t="inlineStr">
         <is>
-          <t>ID63(4D63)</t>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H108" s="9" t="inlineStr">
         <is>
-          <t>막대키</t>
+          <t>폴딩키,스마트키</t>
         </is>
       </c>
       <c r="I108" s="9" t="inlineStr">
         <is>
-          <t>164-R0475[해외 공용 품번]</t>
+          <t>164-R8267[비상키, 해외 공용 품번]</t>
         </is>
       </c>
       <c r="J108" s="9" t="inlineStr">
         <is>
-          <t>FO38</t>
+          <t>HU198</t>
         </is>
       </c>
       <c r="K108" s="9" t="inlineStr"/>
-      <c r="L108" s="9" t="inlineStr"/>
-      <c r="M108" s="9" t="inlineStr"/>
+      <c r="L108" s="9" t="inlineStr">
+        <is>
+          <t>164-R8406[랩터, 해외 공용 품번]</t>
+        </is>
+      </c>
+      <c r="M108" s="9" t="inlineStr">
+        <is>
+          <t>164-R8337[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="N108" s="9" t="inlineStr">
         <is>
           <t>PATS</t>
@@ -7765,1669 +7789,13 @@
       </c>
       <c r="O108" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Ford Catalog Five Hundred 2005–2007·Taurus X 2008–2009 Texas Crypto 4D63 DST40 — 프리스타일은 파이브 헌드레드 왜건형, 트랜스폰더 키 164-R0475)</t>
+          <t>transpondery(Ford Catalog Next-Gen Ranger·Raptor 2023–2025 HiTag Pro ID49, 플립키 164-R8337 434MHz(2025), 랩터 스마트키 164-R8406 434MHz, 센터밀 비상키 164-R8267 HU198), 다나와(신형 레인저 국내 출시)</t>
         </is>
       </c>
       <c r="P108" s="9" t="inlineStr"/>
     </row>
-    <row r="109">
-      <c r="A109" s="9" t="inlineStr">
-        <is>
-          <t>포드</t>
-        </is>
-      </c>
-      <c r="B109" s="9" t="inlineStr">
-        <is>
-          <t>익스페디션</t>
-        </is>
-      </c>
-      <c r="C109" s="9" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="D109" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E109" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F109" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G109" s="6" t="inlineStr">
-        <is>
-          <t>ID4C</t>
-        </is>
-      </c>
-      <c r="H109" s="9" t="inlineStr">
-        <is>
-          <t>막대키</t>
-        </is>
-      </c>
-      <c r="I109" s="9" t="inlineStr">
-        <is>
-          <t>011-R0221[해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="J109" s="9" t="inlineStr">
-        <is>
-          <t>FO38</t>
-        </is>
-      </c>
-      <c r="K109" s="9" t="inlineStr"/>
-      <c r="L109" s="9" t="inlineStr"/>
-      <c r="M109" s="9" t="inlineStr"/>
-      <c r="N109" s="6" t="inlineStr">
-        <is>
-          <t>PATS</t>
-        </is>
-      </c>
-      <c r="O109" s="9" t="inlineStr">
-        <is>
-          <t>transpondery(Ford Catalog Expedition 1997–2002 Texas Fixed 4C, 011-R0221 H72-PT)</t>
-        </is>
-      </c>
-      <c r="P109" s="6" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 이력 없음 — 해외(북미) 사양 기준</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="9" t="inlineStr">
-        <is>
-          <t>포드</t>
-        </is>
-      </c>
-      <c r="B110" s="9" t="inlineStr">
-        <is>
-          <t>익스페디션</t>
-        </is>
-      </c>
-      <c r="C110" s="9" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="D110" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E110" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F110" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G110" s="6" t="inlineStr">
-        <is>
-          <t>ID4C</t>
-        </is>
-      </c>
-      <c r="H110" s="9" t="inlineStr">
-        <is>
-          <t>막대키</t>
-        </is>
-      </c>
-      <c r="I110" s="9" t="inlineStr">
-        <is>
-          <t>011-R0221[해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="J110" s="9" t="inlineStr">
-        <is>
-          <t>FO38</t>
-        </is>
-      </c>
-      <c r="K110" s="9" t="inlineStr"/>
-      <c r="L110" s="9" t="inlineStr"/>
-      <c r="M110" s="9" t="inlineStr"/>
-      <c r="N110" s="6" t="inlineStr">
-        <is>
-          <t>PATS</t>
-        </is>
-      </c>
-      <c r="O110" s="9" t="inlineStr">
-        <is>
-          <t>transpondery(Ford Catalog Expedition 1997–2002 Texas Fixed 4C, 011-R0221 H72-PT)</t>
-        </is>
-      </c>
-      <c r="P110" s="6" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 이력 없음 — 해외(북미) 사양 기준</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="9" t="inlineStr">
-        <is>
-          <t>포드</t>
-        </is>
-      </c>
-      <c r="B111" s="9" t="inlineStr">
-        <is>
-          <t>익스페디션</t>
-        </is>
-      </c>
-      <c r="C111" s="9" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="D111" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E111" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F111" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G111" s="6" t="inlineStr">
-        <is>
-          <t>ID4C</t>
-        </is>
-      </c>
-      <c r="H111" s="9" t="inlineStr">
-        <is>
-          <t>막대키</t>
-        </is>
-      </c>
-      <c r="I111" s="9" t="inlineStr">
-        <is>
-          <t>011-R0221[해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="J111" s="9" t="inlineStr">
-        <is>
-          <t>FO38</t>
-        </is>
-      </c>
-      <c r="K111" s="9" t="inlineStr"/>
-      <c r="L111" s="9" t="inlineStr"/>
-      <c r="M111" s="9" t="inlineStr"/>
-      <c r="N111" s="6" t="inlineStr">
-        <is>
-          <t>PATS</t>
-        </is>
-      </c>
-      <c r="O111" s="9" t="inlineStr">
-        <is>
-          <t>transpondery(Ford Catalog Expedition 1997–2002 Texas Fixed 4C, 011-R0221 H72-PT)</t>
-        </is>
-      </c>
-      <c r="P111" s="6" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 이력 없음 — 해외(북미) 사양 기준</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="9" t="inlineStr">
-        <is>
-          <t>포드</t>
-        </is>
-      </c>
-      <c r="B112" s="9" t="inlineStr">
-        <is>
-          <t>익스페디션</t>
-        </is>
-      </c>
-      <c r="C112" s="9" t="inlineStr">
-        <is>
-          <t>2003</t>
-        </is>
-      </c>
-      <c r="D112" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E112" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F112" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G112" s="6" t="inlineStr">
-        <is>
-          <t>ID60(4D60)</t>
-        </is>
-      </c>
-      <c r="H112" s="9" t="inlineStr">
-        <is>
-          <t>막대키</t>
-        </is>
-      </c>
-      <c r="I112" s="9" t="inlineStr">
-        <is>
-          <t>164-R0475[해외 공용 품번], 164-R8040[해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="J112" s="9" t="inlineStr">
-        <is>
-          <t>FO38</t>
-        </is>
-      </c>
-      <c r="K112" s="9" t="inlineStr"/>
-      <c r="L112" s="9" t="inlineStr"/>
-      <c r="M112" s="9" t="inlineStr"/>
-      <c r="N112" s="6" t="inlineStr">
-        <is>
-          <t>PATS</t>
-        </is>
-      </c>
-      <c r="O112" s="9" t="inlineStr">
-        <is>
-          <t>transpondery(Ford Catalog Expedition 2003–2006 Texas Crypto 4D60, 164-R0475·164-R8040 H84-PT)</t>
-        </is>
-      </c>
-      <c r="P112" s="6" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 이력 없음 — 해외(북미) 사양 기준</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="9" t="inlineStr">
-        <is>
-          <t>포드</t>
-        </is>
-      </c>
-      <c r="B113" s="9" t="inlineStr">
-        <is>
-          <t>익스페디션</t>
-        </is>
-      </c>
-      <c r="C113" s="9" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
-      </c>
-      <c r="D113" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E113" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F113" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G113" s="6" t="inlineStr">
-        <is>
-          <t>ID60(4D60)</t>
-        </is>
-      </c>
-      <c r="H113" s="9" t="inlineStr">
-        <is>
-          <t>막대키</t>
-        </is>
-      </c>
-      <c r="I113" s="9" t="inlineStr">
-        <is>
-          <t>164-R0475[해외 공용 품번], 164-R8040[해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="J113" s="9" t="inlineStr">
-        <is>
-          <t>FO38</t>
-        </is>
-      </c>
-      <c r="K113" s="9" t="inlineStr"/>
-      <c r="L113" s="9" t="inlineStr"/>
-      <c r="M113" s="9" t="inlineStr"/>
-      <c r="N113" s="6" t="inlineStr">
-        <is>
-          <t>PATS</t>
-        </is>
-      </c>
-      <c r="O113" s="9" t="inlineStr">
-        <is>
-          <t>transpondery(Ford Catalog Expedition 2003–2006 Texas Crypto 4D60, 164-R0475·164-R8040 H84-PT)</t>
-        </is>
-      </c>
-      <c r="P113" s="6" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 이력 없음 — 해외(북미) 사양 기준</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="9" t="inlineStr">
-        <is>
-          <t>포드</t>
-        </is>
-      </c>
-      <c r="B114" s="9" t="inlineStr">
-        <is>
-          <t>익스페디션</t>
-        </is>
-      </c>
-      <c r="C114" s="9" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
-      </c>
-      <c r="D114" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E114" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F114" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G114" s="6" t="inlineStr">
-        <is>
-          <t>ID60(4D60)</t>
-        </is>
-      </c>
-      <c r="H114" s="9" t="inlineStr">
-        <is>
-          <t>막대키</t>
-        </is>
-      </c>
-      <c r="I114" s="9" t="inlineStr">
-        <is>
-          <t>164-R0475[해외 공용 품번], 164-R8040[해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="J114" s="9" t="inlineStr">
-        <is>
-          <t>FO38</t>
-        </is>
-      </c>
-      <c r="K114" s="9" t="inlineStr"/>
-      <c r="L114" s="9" t="inlineStr"/>
-      <c r="M114" s="9" t="inlineStr"/>
-      <c r="N114" s="6" t="inlineStr">
-        <is>
-          <t>PATS</t>
-        </is>
-      </c>
-      <c r="O114" s="9" t="inlineStr">
-        <is>
-          <t>transpondery(Ford Catalog Expedition 2003–2006 Texas Crypto 4D60, 164-R0475·164-R8040 H84-PT)</t>
-        </is>
-      </c>
-      <c r="P114" s="6" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 이력 없음 — 해외(북미) 사양 기준</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="9" t="inlineStr">
-        <is>
-          <t>포드</t>
-        </is>
-      </c>
-      <c r="B115" s="9" t="inlineStr">
-        <is>
-          <t>익스페디션</t>
-        </is>
-      </c>
-      <c r="C115" s="9" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
-      </c>
-      <c r="D115" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E115" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F115" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G115" s="6" t="inlineStr">
-        <is>
-          <t>ID60(4D60)</t>
-        </is>
-      </c>
-      <c r="H115" s="9" t="inlineStr">
-        <is>
-          <t>막대키</t>
-        </is>
-      </c>
-      <c r="I115" s="9" t="inlineStr">
-        <is>
-          <t>164-R0475[해외 공용 품번], 164-R8040[해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="J115" s="9" t="inlineStr">
-        <is>
-          <t>FO38</t>
-        </is>
-      </c>
-      <c r="K115" s="9" t="inlineStr"/>
-      <c r="L115" s="9" t="inlineStr"/>
-      <c r="M115" s="9" t="inlineStr"/>
-      <c r="N115" s="6" t="inlineStr">
-        <is>
-          <t>PATS</t>
-        </is>
-      </c>
-      <c r="O115" s="9" t="inlineStr">
-        <is>
-          <t>transpondery(Ford Catalog Expedition 2003–2006 Texas Crypto 4D60, 164-R0475·164-R8040 H84-PT)</t>
-        </is>
-      </c>
-      <c r="P115" s="6" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 이력 없음 — 해외(북미) 사양 기준</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="9" t="inlineStr">
-        <is>
-          <t>포드</t>
-        </is>
-      </c>
-      <c r="B116" s="9" t="inlineStr">
-        <is>
-          <t>익스페디션</t>
-        </is>
-      </c>
-      <c r="C116" s="9" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="D116" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E116" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F116" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G116" s="6" t="inlineStr">
-        <is>
-          <t>ID63(4D63)</t>
-        </is>
-      </c>
-      <c r="H116" s="9" t="inlineStr">
-        <is>
-          <t>막대키</t>
-        </is>
-      </c>
-      <c r="I116" s="9" t="inlineStr"/>
-      <c r="J116" s="9" t="inlineStr">
-        <is>
-          <t>FO38</t>
-        </is>
-      </c>
-      <c r="K116" s="9" t="inlineStr"/>
-      <c r="L116" s="9" t="inlineStr"/>
-      <c r="M116" s="9" t="inlineStr"/>
-      <c r="N116" s="6" t="inlineStr">
-        <is>
-          <t>PATS</t>
-        </is>
-      </c>
-      <c r="O116" s="9" t="inlineStr">
-        <is>
-          <t>transpondery(Ford Catalog Expedition 2006–2010 Texas Crypto 4D63 DST40)</t>
-        </is>
-      </c>
-      <c r="P116" s="6" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 이력 없음 — 해외(북미) 사양 기준</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="9" t="inlineStr">
-        <is>
-          <t>포드</t>
-        </is>
-      </c>
-      <c r="B117" s="9" t="inlineStr">
-        <is>
-          <t>익스페디션</t>
-        </is>
-      </c>
-      <c r="C117" s="9" t="inlineStr">
-        <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="D117" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E117" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F117" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G117" s="6" t="inlineStr">
-        <is>
-          <t>ID63(4D63)</t>
-        </is>
-      </c>
-      <c r="H117" s="9" t="inlineStr">
-        <is>
-          <t>막대키</t>
-        </is>
-      </c>
-      <c r="I117" s="9" t="inlineStr"/>
-      <c r="J117" s="9" t="inlineStr">
-        <is>
-          <t>FO38</t>
-        </is>
-      </c>
-      <c r="K117" s="9" t="inlineStr"/>
-      <c r="L117" s="9" t="inlineStr"/>
-      <c r="M117" s="9" t="inlineStr"/>
-      <c r="N117" s="6" t="inlineStr">
-        <is>
-          <t>PATS</t>
-        </is>
-      </c>
-      <c r="O117" s="9" t="inlineStr">
-        <is>
-          <t>transpondery(Ford Catalog Expedition 2006–2010 Texas Crypto 4D63 DST40)</t>
-        </is>
-      </c>
-      <c r="P117" s="6" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 이력 없음 — 해외(북미) 사양 기준</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="9" t="inlineStr">
-        <is>
-          <t>포드</t>
-        </is>
-      </c>
-      <c r="B118" s="9" t="inlineStr">
-        <is>
-          <t>익스페디션</t>
-        </is>
-      </c>
-      <c r="C118" s="9" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="D118" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E118" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F118" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G118" s="6" t="inlineStr">
-        <is>
-          <t>ID63(4D63)</t>
-        </is>
-      </c>
-      <c r="H118" s="9" t="inlineStr">
-        <is>
-          <t>막대키</t>
-        </is>
-      </c>
-      <c r="I118" s="9" t="inlineStr"/>
-      <c r="J118" s="9" t="inlineStr">
-        <is>
-          <t>FO38</t>
-        </is>
-      </c>
-      <c r="K118" s="9" t="inlineStr"/>
-      <c r="L118" s="9" t="inlineStr"/>
-      <c r="M118" s="9" t="inlineStr"/>
-      <c r="N118" s="6" t="inlineStr">
-        <is>
-          <t>PATS</t>
-        </is>
-      </c>
-      <c r="O118" s="9" t="inlineStr">
-        <is>
-          <t>transpondery(Ford Catalog Expedition 2006–2010 Texas Crypto 4D63 DST40)</t>
-        </is>
-      </c>
-      <c r="P118" s="6" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 이력 없음 — 해외(북미) 사양 기준</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="9" t="inlineStr">
-        <is>
-          <t>포드</t>
-        </is>
-      </c>
-      <c r="B119" s="9" t="inlineStr">
-        <is>
-          <t>익스페디션</t>
-        </is>
-      </c>
-      <c r="C119" s="9" t="inlineStr">
-        <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="D119" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E119" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F119" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G119" s="6" t="inlineStr">
-        <is>
-          <t>ID63(4D63)</t>
-        </is>
-      </c>
-      <c r="H119" s="9" t="inlineStr">
-        <is>
-          <t>막대키</t>
-        </is>
-      </c>
-      <c r="I119" s="9" t="inlineStr"/>
-      <c r="J119" s="9" t="inlineStr">
-        <is>
-          <t>FO38</t>
-        </is>
-      </c>
-      <c r="K119" s="9" t="inlineStr"/>
-      <c r="L119" s="9" t="inlineStr"/>
-      <c r="M119" s="9" t="inlineStr"/>
-      <c r="N119" s="6" t="inlineStr">
-        <is>
-          <t>PATS</t>
-        </is>
-      </c>
-      <c r="O119" s="9" t="inlineStr">
-        <is>
-          <t>transpondery(Ford Catalog Expedition 2006–2010 Texas Crypto 4D63 DST40)</t>
-        </is>
-      </c>
-      <c r="P119" s="6" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 이력 없음 — 해외(북미) 사양 기준</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="9" t="inlineStr">
-        <is>
-          <t>포드</t>
-        </is>
-      </c>
-      <c r="B120" s="9" t="inlineStr">
-        <is>
-          <t>익스페디션</t>
-        </is>
-      </c>
-      <c r="C120" s="9" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="D120" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E120" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F120" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G120" s="6" t="inlineStr">
-        <is>
-          <t>4D63x80</t>
-        </is>
-      </c>
-      <c r="H120" s="9" t="inlineStr">
-        <is>
-          <t>막대키</t>
-        </is>
-      </c>
-      <c r="I120" s="9" t="inlineStr"/>
-      <c r="J120" s="9" t="inlineStr">
-        <is>
-          <t>FO38</t>
-        </is>
-      </c>
-      <c r="K120" s="9" t="inlineStr"/>
-      <c r="L120" s="9" t="inlineStr"/>
-      <c r="M120" s="9" t="inlineStr"/>
-      <c r="N120" s="6" t="inlineStr">
-        <is>
-          <t>PATS</t>
-        </is>
-      </c>
-      <c r="O120" s="9" t="inlineStr">
-        <is>
-          <t>transpondery(Ford Catalog Expedition 2011–2017 DST80 ID63-6F 80bit)</t>
-        </is>
-      </c>
-      <c r="P120" s="6" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 이력 없음 — 해외(북미) 사양 기준</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="9" t="inlineStr">
-        <is>
-          <t>포드</t>
-        </is>
-      </c>
-      <c r="B121" s="9" t="inlineStr">
-        <is>
-          <t>익스페디션</t>
-        </is>
-      </c>
-      <c r="C121" s="9" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="D121" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E121" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F121" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G121" s="6" t="inlineStr">
-        <is>
-          <t>4D63x80</t>
-        </is>
-      </c>
-      <c r="H121" s="9" t="inlineStr">
-        <is>
-          <t>막대키</t>
-        </is>
-      </c>
-      <c r="I121" s="9" t="inlineStr"/>
-      <c r="J121" s="9" t="inlineStr">
-        <is>
-          <t>FO38</t>
-        </is>
-      </c>
-      <c r="K121" s="9" t="inlineStr"/>
-      <c r="L121" s="9" t="inlineStr"/>
-      <c r="M121" s="9" t="inlineStr"/>
-      <c r="N121" s="6" t="inlineStr">
-        <is>
-          <t>PATS</t>
-        </is>
-      </c>
-      <c r="O121" s="9" t="inlineStr">
-        <is>
-          <t>transpondery(Ford Catalog Expedition 2011–2017 DST80 ID63-6F 80bit)</t>
-        </is>
-      </c>
-      <c r="P121" s="6" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 이력 없음 — 해외(북미) 사양 기준</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="9" t="inlineStr">
-        <is>
-          <t>포드</t>
-        </is>
-      </c>
-      <c r="B122" s="9" t="inlineStr">
-        <is>
-          <t>익스페디션</t>
-        </is>
-      </c>
-      <c r="C122" s="9" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="D122" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E122" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F122" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G122" s="6" t="inlineStr">
-        <is>
-          <t>4D63x80</t>
-        </is>
-      </c>
-      <c r="H122" s="9" t="inlineStr">
-        <is>
-          <t>막대키</t>
-        </is>
-      </c>
-      <c r="I122" s="9" t="inlineStr"/>
-      <c r="J122" s="9" t="inlineStr">
-        <is>
-          <t>FO38</t>
-        </is>
-      </c>
-      <c r="K122" s="9" t="inlineStr"/>
-      <c r="L122" s="9" t="inlineStr"/>
-      <c r="M122" s="9" t="inlineStr"/>
-      <c r="N122" s="6" t="inlineStr">
-        <is>
-          <t>PATS</t>
-        </is>
-      </c>
-      <c r="O122" s="9" t="inlineStr">
-        <is>
-          <t>transpondery(Ford Catalog Expedition 2011–2017 DST80 ID63-6F 80bit)</t>
-        </is>
-      </c>
-      <c r="P122" s="6" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 이력 없음 — 해외(북미) 사양 기준</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="9" t="inlineStr">
-        <is>
-          <t>포드</t>
-        </is>
-      </c>
-      <c r="B123" s="9" t="inlineStr">
-        <is>
-          <t>익스페디션</t>
-        </is>
-      </c>
-      <c r="C123" s="9" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="D123" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E123" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F123" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G123" s="6" t="inlineStr">
-        <is>
-          <t>4D63x80</t>
-        </is>
-      </c>
-      <c r="H123" s="9" t="inlineStr">
-        <is>
-          <t>막대키</t>
-        </is>
-      </c>
-      <c r="I123" s="9" t="inlineStr"/>
-      <c r="J123" s="9" t="inlineStr">
-        <is>
-          <t>FO38</t>
-        </is>
-      </c>
-      <c r="K123" s="9" t="inlineStr"/>
-      <c r="L123" s="9" t="inlineStr"/>
-      <c r="M123" s="9" t="inlineStr"/>
-      <c r="N123" s="6" t="inlineStr">
-        <is>
-          <t>PATS</t>
-        </is>
-      </c>
-      <c r="O123" s="9" t="inlineStr">
-        <is>
-          <t>transpondery(Ford Catalog Expedition 2011–2017 DST80 ID63-6F 80bit)</t>
-        </is>
-      </c>
-      <c r="P123" s="6" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 이력 없음 — 해외(북미) 사양 기준</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="9" t="inlineStr">
-        <is>
-          <t>포드</t>
-        </is>
-      </c>
-      <c r="B124" s="9" t="inlineStr">
-        <is>
-          <t>익스페디션</t>
-        </is>
-      </c>
-      <c r="C124" s="9" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="D124" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E124" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F124" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G124" s="6" t="inlineStr">
-        <is>
-          <t>4D63x80[일반 키], ID46(PCF7953A)[스마트키]</t>
-        </is>
-      </c>
-      <c r="H124" s="9" t="inlineStr">
-        <is>
-          <t>막대키,스마트키</t>
-        </is>
-      </c>
-      <c r="I124" s="9" t="inlineStr">
-        <is>
-          <t>164-R8041[비상키, 해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="J124" s="9" t="inlineStr">
-        <is>
-          <t>FO38, HU101</t>
-        </is>
-      </c>
-      <c r="K124" s="9" t="inlineStr"/>
-      <c r="L124" s="9" t="inlineStr"/>
-      <c r="M124" s="9" t="inlineStr"/>
-      <c r="N124" s="6" t="inlineStr">
-        <is>
-          <t>PATS</t>
-        </is>
-      </c>
-      <c r="O124" s="9" t="inlineStr">
-        <is>
-          <t>transpondery(Ford Catalog Expedition 2015–2017 ID46 PCF7953A 스마트키, 비상키 164-R8041), 위키백과(국내는 2021.3.22 4세대부터 판매)</t>
-        </is>
-      </c>
-      <c r="P124" s="6" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 이력 없음 — 해외(북미) 사양 기준</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="9" t="inlineStr">
-        <is>
-          <t>포드</t>
-        </is>
-      </c>
-      <c r="B125" s="9" t="inlineStr">
-        <is>
-          <t>익스페디션</t>
-        </is>
-      </c>
-      <c r="C125" s="9" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="D125" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E125" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F125" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G125" s="6" t="inlineStr">
-        <is>
-          <t>4D63x80[일반 키], ID46(PCF7953A)[스마트키]</t>
-        </is>
-      </c>
-      <c r="H125" s="9" t="inlineStr">
-        <is>
-          <t>막대키,스마트키</t>
-        </is>
-      </c>
-      <c r="I125" s="9" t="inlineStr">
-        <is>
-          <t>164-R8041[비상키, 해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="J125" s="9" t="inlineStr">
-        <is>
-          <t>FO38, HU101</t>
-        </is>
-      </c>
-      <c r="K125" s="9" t="inlineStr"/>
-      <c r="L125" s="9" t="inlineStr"/>
-      <c r="M125" s="9" t="inlineStr"/>
-      <c r="N125" s="6" t="inlineStr">
-        <is>
-          <t>PATS</t>
-        </is>
-      </c>
-      <c r="O125" s="9" t="inlineStr">
-        <is>
-          <t>transpondery(Ford Catalog Expedition 2015–2017 ID46 PCF7953A 스마트키, 비상키 164-R8041), 위키백과(국내는 2021.3.22 4세대부터 판매)</t>
-        </is>
-      </c>
-      <c r="P125" s="6" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 이력 없음 — 해외(북미) 사양 기준</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="9" t="inlineStr">
-        <is>
-          <t>포드</t>
-        </is>
-      </c>
-      <c r="B126" s="9" t="inlineStr">
-        <is>
-          <t>익스페디션</t>
-        </is>
-      </c>
-      <c r="C126" s="9" t="inlineStr">
-        <is>
-          <t>2017(단종)</t>
-        </is>
-      </c>
-      <c r="D126" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E126" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F126" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G126" s="6" t="inlineStr">
-        <is>
-          <t>4D63x80[일반 키], ID46(PCF7953A)[스마트키]</t>
-        </is>
-      </c>
-      <c r="H126" s="9" t="inlineStr">
-        <is>
-          <t>막대키,스마트키</t>
-        </is>
-      </c>
-      <c r="I126" s="9" t="inlineStr">
-        <is>
-          <t>164-R8041[비상키, 해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="J126" s="9" t="inlineStr">
-        <is>
-          <t>FO38, HU101</t>
-        </is>
-      </c>
-      <c r="K126" s="9" t="inlineStr"/>
-      <c r="L126" s="9" t="inlineStr"/>
-      <c r="M126" s="9" t="inlineStr"/>
-      <c r="N126" s="6" t="inlineStr">
-        <is>
-          <t>PATS</t>
-        </is>
-      </c>
-      <c r="O126" s="9" t="inlineStr">
-        <is>
-          <t>transpondery(Ford Catalog Expedition 2015–2017 ID46 PCF7953A 스마트키, 비상키 164-R8041), 위키백과(국내는 2021.3.22 4세대부터 판매)</t>
-        </is>
-      </c>
-      <c r="P126" s="6" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 이력 없음 — 해외(북미) 사양 기준</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="9" t="inlineStr">
-        <is>
-          <t>포드</t>
-        </is>
-      </c>
-      <c r="B127" s="9" t="inlineStr">
-        <is>
-          <t>레인저</t>
-        </is>
-      </c>
-      <c r="C127" s="9" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="D127" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E127" s="4" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F127" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G127" s="9" t="inlineStr">
-        <is>
-          <t>ID49</t>
-        </is>
-      </c>
-      <c r="H127" s="9" t="inlineStr">
-        <is>
-          <t>폴딩키</t>
-        </is>
-      </c>
-      <c r="I127" s="9" t="inlineStr"/>
-      <c r="J127" s="9" t="inlineStr">
-        <is>
-          <t>HU101</t>
-        </is>
-      </c>
-      <c r="K127" s="9" t="inlineStr"/>
-      <c r="L127" s="9" t="inlineStr"/>
-      <c r="M127" s="9" t="inlineStr">
-        <is>
-          <t>EB3T-15K601-BA[해외 공용 품번], EB3T-15K601-BB[해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="N127" s="9" t="inlineStr">
-        <is>
-          <t>PATS</t>
-        </is>
-      </c>
-      <c r="O127" s="9" t="inlineStr">
-        <is>
-          <t>transpondery(Ford Catalog Ranger T6 Facelift 2015–2022 Europe·Australia HiTag Pro ID49, 플립키 EB3T-15K601-BA·BB 434MHz FSK), 아주경제(레인저 2021.4.12 국내 첫 출시)</t>
-        </is>
-      </c>
-      <c r="P127" s="9" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="9" t="inlineStr">
-        <is>
-          <t>포드</t>
-        </is>
-      </c>
-      <c r="B128" s="9" t="inlineStr">
-        <is>
-          <t>레인저</t>
-        </is>
-      </c>
-      <c r="C128" s="9" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="D128" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E128" s="4" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F128" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G128" s="9" t="inlineStr">
-        <is>
-          <t>ID49</t>
-        </is>
-      </c>
-      <c r="H128" s="9" t="inlineStr">
-        <is>
-          <t>폴딩키</t>
-        </is>
-      </c>
-      <c r="I128" s="9" t="inlineStr"/>
-      <c r="J128" s="9" t="inlineStr">
-        <is>
-          <t>HU101</t>
-        </is>
-      </c>
-      <c r="K128" s="9" t="inlineStr"/>
-      <c r="L128" s="9" t="inlineStr"/>
-      <c r="M128" s="9" t="inlineStr">
-        <is>
-          <t>EB3T-15K601-BA[해외 공용 품번], EB3T-15K601-BB[해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="N128" s="9" t="inlineStr">
-        <is>
-          <t>PATS</t>
-        </is>
-      </c>
-      <c r="O128" s="9" t="inlineStr">
-        <is>
-          <t>transpondery(Ford Catalog Ranger T6 Facelift 2015–2022 Europe·Australia HiTag Pro ID49, 플립키 EB3T-15K601-BA·BB 434MHz FSK), 아주경제(레인저 2021.4.12 국내 첫 출시)</t>
-        </is>
-      </c>
-      <c r="P128" s="9" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="9" t="inlineStr">
-        <is>
-          <t>포드</t>
-        </is>
-      </c>
-      <c r="B129" s="9" t="inlineStr">
-        <is>
-          <t>레인저</t>
-        </is>
-      </c>
-      <c r="C129" s="9" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D129" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E129" s="4" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F129" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G129" s="9" t="inlineStr">
-        <is>
-          <t>ID49</t>
-        </is>
-      </c>
-      <c r="H129" s="9" t="inlineStr">
-        <is>
-          <t>폴딩키,스마트키</t>
-        </is>
-      </c>
-      <c r="I129" s="9" t="inlineStr">
-        <is>
-          <t>164-R8267[비상키, 해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="J129" s="9" t="inlineStr">
-        <is>
-          <t>HU198</t>
-        </is>
-      </c>
-      <c r="K129" s="9" t="inlineStr"/>
-      <c r="L129" s="9" t="inlineStr">
-        <is>
-          <t>164-R8406[랩터, 해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="M129" s="9" t="inlineStr">
-        <is>
-          <t>164-R8337[해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="N129" s="9" t="inlineStr">
-        <is>
-          <t>PATS</t>
-        </is>
-      </c>
-      <c r="O129" s="9" t="inlineStr">
-        <is>
-          <t>transpondery(Ford Catalog Next-Gen Ranger·Raptor 2023–2025 HiTag Pro ID49, 플립키 164-R8337 434MHz(2025), 랩터 스마트키 164-R8406 434MHz, 센터밀 비상키 164-R8267 HU198), 다나와(신형 레인저 국내 출시)</t>
-        </is>
-      </c>
-      <c r="P129" s="9" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="9" t="inlineStr">
-        <is>
-          <t>포드</t>
-        </is>
-      </c>
-      <c r="B130" s="9" t="inlineStr">
-        <is>
-          <t>레인저</t>
-        </is>
-      </c>
-      <c r="C130" s="9" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D130" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E130" s="4" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F130" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G130" s="9" t="inlineStr">
-        <is>
-          <t>ID49</t>
-        </is>
-      </c>
-      <c r="H130" s="9" t="inlineStr">
-        <is>
-          <t>폴딩키,스마트키</t>
-        </is>
-      </c>
-      <c r="I130" s="9" t="inlineStr">
-        <is>
-          <t>164-R8267[비상키, 해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="J130" s="9" t="inlineStr">
-        <is>
-          <t>HU198</t>
-        </is>
-      </c>
-      <c r="K130" s="9" t="inlineStr"/>
-      <c r="L130" s="9" t="inlineStr">
-        <is>
-          <t>164-R8406[랩터, 해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="M130" s="9" t="inlineStr">
-        <is>
-          <t>164-R8337[해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="N130" s="9" t="inlineStr">
-        <is>
-          <t>PATS</t>
-        </is>
-      </c>
-      <c r="O130" s="9" t="inlineStr">
-        <is>
-          <t>transpondery(Ford Catalog Next-Gen Ranger·Raptor 2023–2025 HiTag Pro ID49, 플립키 164-R8337 434MHz(2025), 랩터 스마트키 164-R8406 434MHz, 센터밀 비상키 164-R8267 HU198), 다나와(신형 레인저 국내 출시)</t>
-        </is>
-      </c>
-      <c r="P130" s="9" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="9" t="inlineStr">
-        <is>
-          <t>포드</t>
-        </is>
-      </c>
-      <c r="B131" s="9" t="inlineStr">
-        <is>
-          <t>레인저</t>
-        </is>
-      </c>
-      <c r="C131" s="9" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D131" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E131" s="4" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F131" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G131" s="9" t="inlineStr">
-        <is>
-          <t>ID49</t>
-        </is>
-      </c>
-      <c r="H131" s="9" t="inlineStr">
-        <is>
-          <t>폴딩키,스마트키</t>
-        </is>
-      </c>
-      <c r="I131" s="9" t="inlineStr">
-        <is>
-          <t>164-R8267[비상키, 해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="J131" s="9" t="inlineStr">
-        <is>
-          <t>HU198</t>
-        </is>
-      </c>
-      <c r="K131" s="9" t="inlineStr"/>
-      <c r="L131" s="9" t="inlineStr">
-        <is>
-          <t>164-R8406[랩터, 해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="M131" s="9" t="inlineStr">
-        <is>
-          <t>164-R8337[해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="N131" s="9" t="inlineStr">
-        <is>
-          <t>PATS</t>
-        </is>
-      </c>
-      <c r="O131" s="9" t="inlineStr">
-        <is>
-          <t>transpondery(Ford Catalog Next-Gen Ranger·Raptor 2023–2025 HiTag Pro ID49, 플립키 164-R8337 434MHz(2025), 랩터 스마트키 164-R8406 434MHz, 센터밀 비상키 164-R8267 HU198), 다나와(신형 레인저 국내 출시)</t>
-        </is>
-      </c>
-      <c r="P131" s="9" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="9" t="inlineStr">
-        <is>
-          <t>포드</t>
-        </is>
-      </c>
-      <c r="B132" s="9" t="inlineStr">
-        <is>
-          <t>레인저</t>
-        </is>
-      </c>
-      <c r="C132" s="9" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="D132" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E132" s="4" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F132" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G132" s="9" t="inlineStr">
-        <is>
-          <t>ID49</t>
-        </is>
-      </c>
-      <c r="H132" s="9" t="inlineStr">
-        <is>
-          <t>폴딩키,스마트키</t>
-        </is>
-      </c>
-      <c r="I132" s="9" t="inlineStr">
-        <is>
-          <t>164-R8267[비상키, 해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="J132" s="9" t="inlineStr">
-        <is>
-          <t>HU198</t>
-        </is>
-      </c>
-      <c r="K132" s="9" t="inlineStr"/>
-      <c r="L132" s="9" t="inlineStr">
-        <is>
-          <t>164-R8406[랩터, 해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="M132" s="9" t="inlineStr">
-        <is>
-          <t>164-R8337[해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="N132" s="9" t="inlineStr">
-        <is>
-          <t>PATS</t>
-        </is>
-      </c>
-      <c r="O132" s="9" t="inlineStr">
-        <is>
-          <t>transpondery(Ford Catalog Next-Gen Ranger·Raptor 2023–2025 HiTag Pro ID49, 플립키 164-R8337 434MHz(2025), 랩터 스마트키 164-R8406 434MHz, 센터밀 비상키 164-R8267 HU198), 다나와(신형 레인저 국내 출시)</t>
-        </is>
-      </c>
-      <c r="P132" s="9" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:P132"/>
+  <autoFilter ref="A1:P108"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9554,7 +7922,7 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>- 주황색: 추정이거나 자료가 서로 다른 값, 칩 전환 시점을 모르는 연식(전·후 2행), 또는 국내 정식 판매 이력이 없는 모델(해외 사양 기준).</t>
+          <t>- 주황색: 추정이거나 자료가 서로 다른 값, 칩 전환 시점을 모르는 연식(전·후 2행).</t>
         </is>
       </c>
     </row>
@@ -9578,7 +7946,7 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>- 익스페디션: 국내는 2021.3.22 4세대부터 판매 — 목록 세대(1997-2017)는 국내 판매 이력이 없어 주황색 / GT(1·2세대): 포드코리아 정식 판매 이력을 찾지 못해 주황색.</t>
+          <t>- 국내 미출시라 뺀 모델: 익스페디션(목록 1997-2017 — 국내는 2021.3.22 4세대부터 판매, 목록에 4세대 없음), GT 슈퍼카 1·2세대(포드코리아 정식 판매 이력 없음).</t>
         </is>
       </c>
     </row>
